--- a/regularisation_MEAUX_PN01_2025.xlsx
+++ b/regularisation_MEAUX_PN01_2025.xlsx
@@ -7,14 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Récapitulatif 2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Paramètres" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BAT 1 - MEAUX I" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="C1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="C2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="C3" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="C4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Vacance Locative" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Récap Site 2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Récap MEAUX I 2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Récap MEAUX II 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Paramètres" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BAT 1 - MEAUX I" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="C1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="C2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="C3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="C4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Vacance Locative" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +691,7 @@
     <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MEAUX PN01 — RÉCAPITULATIF DES CHARGES 2025</t>
+          <t>MEAUX PN01 — CHARGES SITE 2025</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1445,443 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.55" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>MEAUX PN01 — COÛT DE LA VACANCE LOCATIVE 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.8" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Estimation de la perte de charges non récupérées sur les lots vacants</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Surface (m²)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>QP annuelle (€ HT)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Période (j/365)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Coût vacance (€ HT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="40">
+        <f>Paramètres!A7</f>
+        <v/>
+      </c>
+      <c r="B5" s="18">
+        <f>Paramètres!B7</f>
+        <v/>
+      </c>
+      <c r="C5" s="41">
+        <f>Paramètres!C7</f>
+        <v/>
+      </c>
+      <c r="D5" s="32">
+        <f>'BAT 1 - MEAUX I'!D39</f>
+        <v/>
+      </c>
+      <c r="E5" s="33">
+        <f>Paramètres!H7/365</f>
+        <v/>
+      </c>
+      <c r="F5" s="28">
+        <f>IF(Paramètres!B7="Vacant",'BAT 1 - MEAUX I'!D39,'BAT 1 - MEAUX I'!D39-'BAT 1 - MEAUX I'!F39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="40">
+        <f>Paramètres!A8</f>
+        <v/>
+      </c>
+      <c r="B6" s="18">
+        <f>Paramètres!B8</f>
+        <v/>
+      </c>
+      <c r="C6" s="41">
+        <f>Paramètres!C8</f>
+        <v/>
+      </c>
+      <c r="D6" s="32">
+        <f>'C1'!D39</f>
+        <v/>
+      </c>
+      <c r="E6" s="33">
+        <f>Paramètres!H8/365</f>
+        <v/>
+      </c>
+      <c r="F6" s="28">
+        <f>IF(Paramètres!B8="Vacant",'C1'!D39,'C1'!D39-'C1'!F39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="40">
+        <f>Paramètres!A9</f>
+        <v/>
+      </c>
+      <c r="B7" s="18">
+        <f>Paramètres!B9</f>
+        <v/>
+      </c>
+      <c r="C7" s="41">
+        <f>Paramètres!C9</f>
+        <v/>
+      </c>
+      <c r="D7" s="32">
+        <f>'C2'!D39</f>
+        <v/>
+      </c>
+      <c r="E7" s="33">
+        <f>Paramètres!H9/365</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>IF(Paramètres!B9="Vacant",'C2'!D39,'C2'!D39-'C2'!F39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="40">
+        <f>Paramètres!A10</f>
+        <v/>
+      </c>
+      <c r="B8" s="18">
+        <f>Paramètres!B10</f>
+        <v/>
+      </c>
+      <c r="C8" s="41">
+        <f>Paramètres!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="32">
+        <f>'C3'!D39</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>Paramètres!H10/365</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>IF(Paramètres!B10="Vacant",'C3'!D39,'C3'!D39-'C3'!F39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40">
+        <f>Paramètres!A11</f>
+        <v/>
+      </c>
+      <c r="B9" s="18">
+        <f>Paramètres!B11</f>
+        <v/>
+      </c>
+      <c r="C9" s="41">
+        <f>Paramètres!C11</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>'C4'!D39</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
+        <f>Paramètres!H11/365</f>
+        <v/>
+      </c>
+      <c r="F9" s="28">
+        <f>IF(Paramètres!B11="Vacant",'C4'!D39,'C4'!D39-'C4'!F39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Total QP charges (tous lots)</t>
+        </is>
+      </c>
+      <c r="D11" s="8">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Nombre de lots vacants</t>
+        </is>
+      </c>
+      <c r="D12" s="42">
+        <f>COUNTIF(B5:B9,"Vacant")</f>
+        <v/>
+      </c>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="34" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1"/>
+    <row r="14" ht="19.55" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Charges non récupérables (Frais Bancaires + CAPEX)</t>
+        </is>
+      </c>
+      <c r="F14" s="44">
+        <f>'Récap Site 2025'!E50+'Récap Site 2025'!E53+'Récap Site 2025'!E56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="25.55" customHeight="1">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>TOTAL COÛT DE LA VACANCE LOCATIVE (€ HT)</t>
+        </is>
+      </c>
+      <c r="F16" s="46">
+        <f>F5+F6+F7+F8+F9+F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="19.55" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Part vacance sur total charges site</t>
+        </is>
+      </c>
+      <c r="F18" s="47">
+        <f>IF(D11&gt;0,F16/D11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20" ht="27.75" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>ℹ  QP annuelle = Total site HT × clé de répartition. Coût vacance = QP annuelle × fraction de l'année non occupée.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A18:E18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MEAUX PN01 — MEAUX I 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.8" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Site : MEAUX PN01  |  Période : 01/01/2025 – 31/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.55" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Date facture</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>N° facture</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Montant HT (€)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>TVA (€)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Montant TTC (€)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MEAUX PN01 — MEAUX II 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.8" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Site : MEAUX PN01  |  Période : 01/01/2025 – 31/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.55" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Fournisseur</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Date facture</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>N° facture</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Montant HT (€)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>TVA (€)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Montant TTC (€)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1781,7 +2219,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Poste (lié au Récapitulatif)</t>
+          <t>Poste (lié aux Récapitulatifs)</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -1792,241 +2230,241 @@
     </row>
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A7,FIND(" — ",'Récapitulatif 2025'!A7)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A7,FIND(" — ",'Récap Site 2025'!A7)+4,100),"")</f>
         <v/>
       </c>
       <c r="C14" s="28">
-        <f>'Récapitulatif 2025'!E7</f>
+        <f>'Récap Site 2025'!E7</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A10,FIND(" — ",'Récapitulatif 2025'!A10)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A10,FIND(" — ",'Récap Site 2025'!A10)+4,100),"")</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>'Récapitulatif 2025'!E10</f>
+        <f>'Récap Site 2025'!E10</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A13,FIND(" — ",'Récapitulatif 2025'!A13)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A13,FIND(" — ",'Récap Site 2025'!A13)+4,100),"")</f>
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>'Récapitulatif 2025'!E13</f>
+        <f>'Récap Site 2025'!E13</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A16,FIND(" — ",'Récapitulatif 2025'!A16)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A16,FIND(" — ",'Récap Site 2025'!A16)+4,100),"")</f>
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>'Récapitulatif 2025'!E16</f>
+        <f>'Récap Site 2025'!E16</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A19,FIND(" — ",'Récapitulatif 2025'!A19)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A19,FIND(" — ",'Récap Site 2025'!A19)+4,100),"")</f>
         <v/>
       </c>
       <c r="C18" s="28">
-        <f>'Récapitulatif 2025'!E19</f>
+        <f>'Récap Site 2025'!E19</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A22,FIND(" — ",'Récapitulatif 2025'!A22)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A22,FIND(" — ",'Récap Site 2025'!A22)+4,100),"")</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>'Récapitulatif 2025'!E22</f>
+        <f>'Récap Site 2025'!E22</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15.05" customHeight="1">
       <c r="A20" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A25,FIND(" — ",'Récapitulatif 2025'!A25)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A25,FIND(" — ",'Récap Site 2025'!A25)+4,100),"")</f>
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>'Récapitulatif 2025'!E25</f>
+        <f>'Récap Site 2025'!E25</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15.05" customHeight="1">
       <c r="A21" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A28,FIND(" — ",'Récapitulatif 2025'!A28)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A28,FIND(" — ",'Récap Site 2025'!A28)+4,100),"")</f>
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>'Récapitulatif 2025'!E28</f>
+        <f>'Récap Site 2025'!E28</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15.05" customHeight="1">
       <c r="A22" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A31,FIND(" — ",'Récapitulatif 2025'!A31)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A31,FIND(" — ",'Récap Site 2025'!A31)+4,100),"")</f>
         <v/>
       </c>
       <c r="C22" s="28">
-        <f>'Récapitulatif 2025'!E31</f>
+        <f>'Récap Site 2025'!E31</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A34,FIND(" — ",'Récapitulatif 2025'!A34)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A34,FIND(" — ",'Récap Site 2025'!A34)+4,100),"")</f>
         <v/>
       </c>
       <c r="C23" s="28">
-        <f>'Récapitulatif 2025'!E34</f>
+        <f>'Récap Site 2025'!E34</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A37,FIND(" — ",'Récapitulatif 2025'!A37)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A37,FIND(" — ",'Récap Site 2025'!A37)+4,100),"")</f>
         <v/>
       </c>
       <c r="C24" s="28">
-        <f>'Récapitulatif 2025'!E37</f>
+        <f>'Récap Site 2025'!E37</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A40,FIND(" — ",'Récapitulatif 2025'!A40)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A40,FIND(" — ",'Récap Site 2025'!A40)+4,100),"")</f>
         <v/>
       </c>
       <c r="C25" s="28">
-        <f>'Récapitulatif 2025'!E40</f>
+        <f>'Récap Site 2025'!E40</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15.05" customHeight="1">
       <c r="A26" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A43,FIND(" — ",'Récapitulatif 2025'!A43)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A43,FIND(" — ",'Récap Site 2025'!A43)+4,100),"")</f>
         <v/>
       </c>
       <c r="C26" s="28">
-        <f>'Récapitulatif 2025'!E43</f>
+        <f>'Récap Site 2025'!E43</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15.05" customHeight="1">
       <c r="A27" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A46,FIND(" — ",'Récapitulatif 2025'!A46)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A46,FIND(" — ",'Récap Site 2025'!A46)+4,100),"")</f>
         <v/>
       </c>
       <c r="C27" s="28">
-        <f>'Récapitulatif 2025'!E46</f>
+        <f>'Récap Site 2025'!E46</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15.05" customHeight="1">
       <c r="A28" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A50,FIND(" — ",'Récapitulatif 2025'!A50)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A50,FIND(" — ",'Récap Site 2025'!A50)+4,100),"")</f>
         <v/>
       </c>
       <c r="C28" s="28">
-        <f>'Récapitulatif 2025'!E50</f>
+        <f>'Récap Site 2025'!E50</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
       <c r="A29" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A53,FIND(" — ",'Récapitulatif 2025'!A53)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A53,FIND(" — ",'Récap Site 2025'!A53)+4,100),"")</f>
         <v/>
       </c>
       <c r="C29" s="28">
-        <f>'Récapitulatif 2025'!E53</f>
+        <f>'Récap Site 2025'!E53</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15.05" customHeight="1">
       <c r="A30" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A56,FIND(" — ",'Récapitulatif 2025'!A56)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A56,FIND(" — ",'Récap Site 2025'!A56)+4,100),"")</f>
         <v/>
       </c>
       <c r="C30" s="28">
-        <f>'Récapitulatif 2025'!E56</f>
+        <f>'Récap Site 2025'!E56</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15.05" customHeight="1">
       <c r="A31" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A60,FIND(" — ",'Récapitulatif 2025'!A60)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A60,FIND(" — ",'Récap Site 2025'!A60)+4,100),"")</f>
         <v/>
       </c>
       <c r="C31" s="28">
-        <f>'Récapitulatif 2025'!E60</f>
+        <f>'Récap Site 2025'!E60</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15.05" customHeight="1">
       <c r="A32" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A63,FIND(" — ",'Récapitulatif 2025'!A63)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A63,FIND(" — ",'Récap Site 2025'!A63)+4,100),"")</f>
         <v/>
       </c>
       <c r="C32" s="28">
-        <f>'Récapitulatif 2025'!E63</f>
+        <f>'Récap Site 2025'!E63</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15.05" customHeight="1">
       <c r="A33" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A66,FIND(" — ",'Récapitulatif 2025'!A66)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A66,FIND(" — ",'Récap Site 2025'!A66)+4,100),"")</f>
         <v/>
       </c>
       <c r="C33" s="28">
-        <f>'Récapitulatif 2025'!E66</f>
+        <f>'Récap Site 2025'!E66</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15.05" customHeight="1">
       <c r="A34" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A69,FIND(" — ",'Récapitulatif 2025'!A69)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A69,FIND(" — ",'Récap Site 2025'!A69)+4,100),"")</f>
         <v/>
       </c>
       <c r="C34" s="28">
-        <f>'Récapitulatif 2025'!E69</f>
+        <f>'Récap Site 2025'!E69</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
       <c r="A35" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A73,FIND(" — ",'Récapitulatif 2025'!A73)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A73,FIND(" — ",'Récap Site 2025'!A73)+4,100),"")</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>'Récapitulatif 2025'!E73</f>
+        <f>'Récap Site 2025'!E73</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15.05" customHeight="1">
       <c r="A36" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A77,FIND(" — ",'Récapitulatif 2025'!A77)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A77,FIND(" — ",'Récap Site 2025'!A77)+4,100),"")</f>
         <v/>
       </c>
       <c r="C36" s="28">
-        <f>'Récapitulatif 2025'!E77</f>
+        <f>'Récap Site 2025'!E77</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15.05" customHeight="1">
       <c r="A37" s="27">
-        <f>IFERROR(MID('Récapitulatif 2025'!A81,FIND(" — ",'Récapitulatif 2025'!A81)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A81,FIND(" — ",'Récap Site 2025'!A81)+4,100),"")</f>
         <v/>
       </c>
       <c r="C37" s="28">
-        <f>'Récapitulatif 2025'!E81</f>
+        <f>'Récap Site 2025'!E81</f>
         <v/>
       </c>
     </row>
@@ -2039,13 +2477,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2088,7 +2526,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Total site HT</t>
+          <t>Total HT</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2107,44 +2545,24 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>CHARGES SITE — MEAUX PN01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CONTRAT MAINTENANCE</t>
         </is>
-      </c>
-    </row>
-    <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>Portails + Barrières automatiques</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>'Récapitulatif 2025'!E7</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>D6*E6</f>
-        <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B7" s="31">
@@ -2152,7 +2570,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récapitulatif 2025'!E34</f>
+        <f>'Récap Site 2025'!E7</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -2171,7 +2589,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Vérifications règlementaires</t>
+          <t>Séparateur hydro.</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -2179,7 +2597,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récapitulatif 2025'!E10</f>
+        <f>'Récap Site 2025'!E34</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -2198,7 +2616,7 @@
     <row r="9" ht="15.05" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Ascenseur</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B9" s="31">
@@ -2206,7 +2624,7 @@
         <v/>
       </c>
       <c r="C9" s="32">
-        <f>'Récapitulatif 2025'!E13</f>
+        <f>'Récap Site 2025'!E10</f>
         <v/>
       </c>
       <c r="D9" s="32">
@@ -2225,7 +2643,7 @@
     <row r="10" ht="15.05" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>Chaufferie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B10" s="31">
@@ -2233,7 +2651,7 @@
         <v/>
       </c>
       <c r="C10" s="32">
-        <f>'Récapitulatif 2025'!E16</f>
+        <f>'Récap Site 2025'!E13</f>
         <v/>
       </c>
       <c r="D10" s="32">
@@ -2252,7 +2670,7 @@
     <row r="11" ht="15.05" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Désenfumage</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B11" s="31">
@@ -2260,7 +2678,7 @@
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>'Récapitulatif 2025'!E19</f>
+        <f>'Récap Site 2025'!E16</f>
         <v/>
       </c>
       <c r="D11" s="32">
@@ -2279,7 +2697,7 @@
     <row r="12" ht="15.05" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Désenfumage</t>
         </is>
       </c>
       <c r="B12" s="31">
@@ -2287,7 +2705,7 @@
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>'Récapitulatif 2025'!E22</f>
+        <f>'Récap Site 2025'!E19</f>
         <v/>
       </c>
       <c r="D12" s="32">
@@ -2306,7 +2724,7 @@
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Espaces verts</t>
         </is>
       </c>
       <c r="B13" s="31">
@@ -2314,7 +2732,7 @@
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récapitulatif 2025'!E25</f>
+        <f>'Récap Site 2025'!E22</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -2333,7 +2751,7 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Portes Coupe-Feu</t>
         </is>
       </c>
       <c r="B14" s="31">
@@ -2341,7 +2759,7 @@
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récapitulatif 2025'!E28</f>
+        <f>'Récap Site 2025'!E25</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -2360,7 +2778,7 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Protection foudre</t>
         </is>
       </c>
       <c r="B15" s="31">
@@ -2368,7 +2786,7 @@
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récapitulatif 2025'!E31</f>
+        <f>'Récap Site 2025'!E28</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -2387,7 +2805,7 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B16" s="31">
@@ -2395,7 +2813,7 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récapitulatif 2025'!E37</f>
+        <f>'Récap Site 2025'!E31</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -2414,7 +2832,7 @@
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>Sprinklers - RIA - PI - Fioul</t>
         </is>
       </c>
       <c r="B17" s="31">
@@ -2422,7 +2840,7 @@
         <v/>
       </c>
       <c r="C17" s="32">
-        <f>'Récapitulatif 2025'!E40</f>
+        <f>'Récap Site 2025'!E37</f>
         <v/>
       </c>
       <c r="D17" s="32">
@@ -2441,7 +2859,7 @@
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B18" s="31">
@@ -2449,7 +2867,7 @@
         <v/>
       </c>
       <c r="C18" s="32">
-        <f>'Récapitulatif 2025'!E43</f>
+        <f>'Récap Site 2025'!E40</f>
         <v/>
       </c>
       <c r="D18" s="32">
@@ -2468,7 +2886,7 @@
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Toiture</t>
+          <t>Télésurveillance</t>
         </is>
       </c>
       <c r="B19" s="31">
@@ -2476,7 +2894,7 @@
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récapitulatif 2025'!E46</f>
+        <f>'Récap Site 2025'!E43</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -2492,64 +2910,64 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>'Récap Site 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>Paramètres!$J$7/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sous-total — CONTRAT MAINTENANCE</t>
         </is>
       </c>
-      <c r="C20" s="8">
-        <f>SUM(C6:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>SUM(D6:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="8">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="8">
+        <f>SUM(C7:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>SUM(D7:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="8">
+        <f>SUM(F7:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>FLUIDES</t>
         </is>
-      </c>
-    </row>
-    <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C22" s="32">
-        <f>'Récapitulatif 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D22" s="32">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>Paramètres!$H$7/365</f>
-        <v/>
-      </c>
-      <c r="F22" s="32">
-        <f>D22*E22</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B23" s="31">
@@ -2557,7 +2975,7 @@
         <v/>
       </c>
       <c r="C23" s="32">
-        <f>'Récapitulatif 2025'!E63</f>
+        <f>'Récap Site 2025'!E60</f>
         <v/>
       </c>
       <c r="D23" s="32">
@@ -2576,7 +2994,7 @@
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B24" s="31">
@@ -2584,7 +3002,7 @@
         <v/>
       </c>
       <c r="C24" s="32">
-        <f>'Récapitulatif 2025'!E66</f>
+        <f>'Récap Site 2025'!E63</f>
         <v/>
       </c>
       <c r="D24" s="32">
@@ -2603,7 +3021,7 @@
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B25" s="31">
@@ -2611,7 +3029,7 @@
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récapitulatif 2025'!E69</f>
+        <f>'Récap Site 2025'!E66</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -2627,328 +3045,357 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="15.05" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C26" s="32">
+        <f>'Récap Site 2025'!E69</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="33">
+        <f>Paramètres!$H$7/365</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sous-total — FLUIDES</t>
         </is>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="8">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="8">
+        <f>SUM(C23:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="8">
+        <f>SUM(D23:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="8">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TAXES</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="29" ht="15.05" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Taxe Bureau &amp; Stationnement</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B29" s="31">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="32">
-        <f>'Récapitulatif 2025'!E73</f>
-        <v/>
-      </c>
-      <c r="D28" s="32">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="33">
+      <c r="C29" s="32">
+        <f>'Récap Site 2025'!E73</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="33">
         <f>Paramètres!$J$7/365</f>
         <v/>
       </c>
-      <c r="F28" s="32">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="F29" s="32">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TAXES</t>
         </is>
       </c>
-      <c r="C29" s="8">
-        <f>SUM(C28:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="8">
-        <f>SUM(D28:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="8">
-        <f>SUM(F28:F28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C30" s="8">
+        <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>SUM(D29:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="8">
+        <f>SUM(F29:F29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>HONORAIRES</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.05" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>Honoraires Divers</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B32" s="31">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C31" s="32">
-        <f>'Récapitulatif 2025'!E77</f>
-        <v/>
-      </c>
-      <c r="D31" s="32">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="33">
+      <c r="C32" s="32">
+        <f>'Récap Site 2025'!E77</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="33">
         <f>Paramètres!$J$7/365</f>
         <v/>
       </c>
-      <c r="F31" s="32">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="F32" s="32">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Sous-total — HONORAIRES</t>
         </is>
       </c>
-      <c r="C32" s="8">
-        <f>SUM(C31:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>SUM(D31:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="8">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C33" s="8">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="8">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TRAVAUX</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.05" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="35" ht="15.05" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>Paramètres!$C$7/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C34" s="32">
-        <f>'Récapitulatif 2025'!E81</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>B34*C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="33">
+      <c r="C35" s="32">
+        <f>'Récap Site 2025'!E81</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>B35*C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="33">
         <f>Paramètres!$J$7/365</f>
         <v/>
       </c>
-      <c r="F34" s="32">
-        <f>D34*E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F35" s="32">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TRAVAUX</t>
         </is>
       </c>
-      <c r="C35" s="8">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="8">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="8">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="7.55" customHeight="1"/>
-    <row r="37" ht="21.75" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="C36" s="8">
+        <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="8">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="7.55" customHeight="1"/>
+    <row r="39" ht="21.75" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C37" s="14">
-        <f>C20+C26+C29+C32+C35</f>
-        <v/>
-      </c>
-      <c r="D37" s="14">
-        <f>D20+D26+D29+D32+D35</f>
-        <v/>
-      </c>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="14">
-        <f>F20+F26+F29+F32+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="19.55" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="C39" s="14">
+        <f>C21+C27+C30+C33+C36</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>D21+D27+D30+D33+D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="14">
+        <f>F21+F27+F30+F33+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="7.55" customHeight="1"/>
+    <row r="41" ht="19.55" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.8" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.8" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.8" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.8" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.8" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.8" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D44" s="8">
-        <f>SUM(D40:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="8">
-        <f>SUM(F40:F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="7.55" customHeight="1"/>
-    <row r="46" ht="21.75" customHeight="1">
-      <c r="A46" s="37">
-        <f>IF(F37-F44&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D46" s="38">
-        <f>D37-D44</f>
-        <v/>
-      </c>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="38">
-        <f>F37-F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="D46" s="8">
+        <f>SUM(D42:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="8">
+        <f>SUM(F42:F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="7.55" customHeight="1"/>
+    <row r="48" ht="21.75" customHeight="1">
+      <c r="A48" s="37">
+        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D48" s="38">
+        <f>D39-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="38">
+        <f>F39-F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="27.75" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2991,7 +3438,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Total site HT</t>
+          <t>Total HT</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3010,44 +3457,24 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>CHARGES SITE — MEAUX PN01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CONTRAT MAINTENANCE</t>
         </is>
-      </c>
-    </row>
-    <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>Portails + Barrières automatiques</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>'Récapitulatif 2025'!E7</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>D6*E6</f>
-        <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B7" s="31">
@@ -3055,7 +3482,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récapitulatif 2025'!E34</f>
+        <f>'Récap Site 2025'!E7</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -3074,7 +3501,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Vérifications règlementaires</t>
+          <t>Séparateur hydro.</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -3082,7 +3509,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récapitulatif 2025'!E10</f>
+        <f>'Récap Site 2025'!E34</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -3101,7 +3528,7 @@
     <row r="9" ht="15.05" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Ascenseur</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B9" s="31">
@@ -3109,7 +3536,7 @@
         <v/>
       </c>
       <c r="C9" s="32">
-        <f>'Récapitulatif 2025'!E13</f>
+        <f>'Récap Site 2025'!E10</f>
         <v/>
       </c>
       <c r="D9" s="32">
@@ -3128,7 +3555,7 @@
     <row r="10" ht="15.05" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>Chaufferie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B10" s="31">
@@ -3136,7 +3563,7 @@
         <v/>
       </c>
       <c r="C10" s="32">
-        <f>'Récapitulatif 2025'!E16</f>
+        <f>'Récap Site 2025'!E13</f>
         <v/>
       </c>
       <c r="D10" s="32">
@@ -3155,7 +3582,7 @@
     <row r="11" ht="15.05" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Désenfumage</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B11" s="31">
@@ -3163,7 +3590,7 @@
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>'Récapitulatif 2025'!E19</f>
+        <f>'Récap Site 2025'!E16</f>
         <v/>
       </c>
       <c r="D11" s="32">
@@ -3182,7 +3609,7 @@
     <row r="12" ht="15.05" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Désenfumage</t>
         </is>
       </c>
       <c r="B12" s="31">
@@ -3190,7 +3617,7 @@
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>'Récapitulatif 2025'!E22</f>
+        <f>'Récap Site 2025'!E19</f>
         <v/>
       </c>
       <c r="D12" s="32">
@@ -3209,7 +3636,7 @@
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Espaces verts</t>
         </is>
       </c>
       <c r="B13" s="31">
@@ -3217,7 +3644,7 @@
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récapitulatif 2025'!E25</f>
+        <f>'Récap Site 2025'!E22</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -3236,7 +3663,7 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Portes Coupe-Feu</t>
         </is>
       </c>
       <c r="B14" s="31">
@@ -3244,7 +3671,7 @@
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récapitulatif 2025'!E28</f>
+        <f>'Récap Site 2025'!E25</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -3263,7 +3690,7 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Protection foudre</t>
         </is>
       </c>
       <c r="B15" s="31">
@@ -3271,7 +3698,7 @@
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récapitulatif 2025'!E31</f>
+        <f>'Récap Site 2025'!E28</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -3290,7 +3717,7 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B16" s="31">
@@ -3298,7 +3725,7 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récapitulatif 2025'!E37</f>
+        <f>'Récap Site 2025'!E31</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -3317,7 +3744,7 @@
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>Sprinklers - RIA - PI - Fioul</t>
         </is>
       </c>
       <c r="B17" s="31">
@@ -3325,7 +3752,7 @@
         <v/>
       </c>
       <c r="C17" s="32">
-        <f>'Récapitulatif 2025'!E40</f>
+        <f>'Récap Site 2025'!E37</f>
         <v/>
       </c>
       <c r="D17" s="32">
@@ -3344,7 +3771,7 @@
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B18" s="31">
@@ -3352,7 +3779,7 @@
         <v/>
       </c>
       <c r="C18" s="32">
-        <f>'Récapitulatif 2025'!E43</f>
+        <f>'Récap Site 2025'!E40</f>
         <v/>
       </c>
       <c r="D18" s="32">
@@ -3371,7 +3798,7 @@
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Toiture</t>
+          <t>Télésurveillance</t>
         </is>
       </c>
       <c r="B19" s="31">
@@ -3379,7 +3806,7 @@
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récapitulatif 2025'!E46</f>
+        <f>'Récap Site 2025'!E43</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -3395,64 +3822,64 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>'Récap Site 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sous-total — CONTRAT MAINTENANCE</t>
         </is>
       </c>
-      <c r="C20" s="8">
-        <f>SUM(C6:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>SUM(D6:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="8">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="8">
+        <f>SUM(C7:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>SUM(D7:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="8">
+        <f>SUM(F7:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>FLUIDES</t>
         </is>
-      </c>
-    </row>
-    <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C22" s="32">
-        <f>'Récapitulatif 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D22" s="32">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>Paramètres!$H$8/365</f>
-        <v/>
-      </c>
-      <c r="F22" s="32">
-        <f>D22*E22</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B23" s="31">
@@ -3460,7 +3887,7 @@
         <v/>
       </c>
       <c r="C23" s="32">
-        <f>'Récapitulatif 2025'!E63</f>
+        <f>'Récap Site 2025'!E60</f>
         <v/>
       </c>
       <c r="D23" s="32">
@@ -3479,7 +3906,7 @@
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B24" s="31">
@@ -3487,7 +3914,7 @@
         <v/>
       </c>
       <c r="C24" s="32">
-        <f>'Récapitulatif 2025'!E66</f>
+        <f>'Récap Site 2025'!E63</f>
         <v/>
       </c>
       <c r="D24" s="32">
@@ -3506,7 +3933,7 @@
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B25" s="31">
@@ -3514,7 +3941,7 @@
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récapitulatif 2025'!E69</f>
+        <f>'Récap Site 2025'!E66</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -3530,328 +3957,357 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="15.05" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C26" s="32">
+        <f>'Récap Site 2025'!E69</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="33">
+        <f>Paramètres!$H$8/365</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sous-total — FLUIDES</t>
         </is>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="8">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="8">
+        <f>SUM(C23:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="8">
+        <f>SUM(D23:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="8">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TAXES</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="29" ht="15.05" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Taxe Bureau &amp; Stationnement</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B29" s="31">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="32">
-        <f>'Récapitulatif 2025'!E73</f>
-        <v/>
-      </c>
-      <c r="D28" s="32">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="33">
+      <c r="C29" s="32">
+        <f>'Récap Site 2025'!E73</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="33">
         <f>Paramètres!$J$8/365</f>
         <v/>
       </c>
-      <c r="F28" s="32">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="F29" s="32">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TAXES</t>
         </is>
       </c>
-      <c r="C29" s="8">
-        <f>SUM(C28:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="8">
-        <f>SUM(D28:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="8">
-        <f>SUM(F28:F28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C30" s="8">
+        <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>SUM(D29:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="8">
+        <f>SUM(F29:F29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>HONORAIRES</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.05" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>Honoraires Divers</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B32" s="31">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C31" s="32">
-        <f>'Récapitulatif 2025'!E77</f>
-        <v/>
-      </c>
-      <c r="D31" s="32">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="33">
+      <c r="C32" s="32">
+        <f>'Récap Site 2025'!E77</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="33">
         <f>Paramètres!$J$8/365</f>
         <v/>
       </c>
-      <c r="F31" s="32">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="F32" s="32">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Sous-total — HONORAIRES</t>
         </is>
       </c>
-      <c r="C32" s="8">
-        <f>SUM(C31:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>SUM(D31:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="8">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C33" s="8">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="8">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TRAVAUX</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.05" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="35" ht="15.05" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>Paramètres!$C$8/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C34" s="32">
-        <f>'Récapitulatif 2025'!E81</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>B34*C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="33">
+      <c r="C35" s="32">
+        <f>'Récap Site 2025'!E81</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>B35*C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="33">
         <f>Paramètres!$J$8/365</f>
         <v/>
       </c>
-      <c r="F34" s="32">
-        <f>D34*E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F35" s="32">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TRAVAUX</t>
         </is>
       </c>
-      <c r="C35" s="8">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="8">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="8">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="7.55" customHeight="1"/>
-    <row r="37" ht="21.75" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="C36" s="8">
+        <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="8">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="7.55" customHeight="1"/>
+    <row r="39" ht="21.75" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C37" s="14">
-        <f>C20+C26+C29+C32+C35</f>
-        <v/>
-      </c>
-      <c r="D37" s="14">
-        <f>D20+D26+D29+D32+D35</f>
-        <v/>
-      </c>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="14">
-        <f>F20+F26+F29+F32+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="19.55" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="C39" s="14">
+        <f>C21+C27+C30+C33+C36</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>D21+D27+D30+D33+D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="14">
+        <f>F21+F27+F30+F33+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="7.55" customHeight="1"/>
+    <row r="41" ht="19.55" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.8" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.8" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.8" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.8" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.8" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.8" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D44" s="8">
-        <f>SUM(D40:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="8">
-        <f>SUM(F40:F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="7.55" customHeight="1"/>
-    <row r="46" ht="21.75" customHeight="1">
-      <c r="A46" s="37">
-        <f>IF(F37-F44&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D46" s="38">
-        <f>D37-D44</f>
-        <v/>
-      </c>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="38">
-        <f>F37-F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="D46" s="8">
+        <f>SUM(D42:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="8">
+        <f>SUM(F42:F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="7.55" customHeight="1"/>
+    <row r="48" ht="21.75" customHeight="1">
+      <c r="A48" s="37">
+        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D48" s="38">
+        <f>D39-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="38">
+        <f>F39-F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="27.75" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3894,7 +4350,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Total site HT</t>
+          <t>Total HT</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3913,44 +4369,24 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>CHARGES SITE — MEAUX PN01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CONTRAT MAINTENANCE</t>
         </is>
-      </c>
-    </row>
-    <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>Portails + Barrières automatiques</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>'Récapitulatif 2025'!E7</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>D6*E6</f>
-        <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B7" s="31">
@@ -3958,7 +4394,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récapitulatif 2025'!E34</f>
+        <f>'Récap Site 2025'!E7</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -3977,7 +4413,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Vérifications règlementaires</t>
+          <t>Séparateur hydro.</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -3985,7 +4421,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récapitulatif 2025'!E10</f>
+        <f>'Récap Site 2025'!E34</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -4004,7 +4440,7 @@
     <row r="9" ht="15.05" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Ascenseur</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B9" s="31">
@@ -4012,7 +4448,7 @@
         <v/>
       </c>
       <c r="C9" s="32">
-        <f>'Récapitulatif 2025'!E13</f>
+        <f>'Récap Site 2025'!E10</f>
         <v/>
       </c>
       <c r="D9" s="32">
@@ -4031,7 +4467,7 @@
     <row r="10" ht="15.05" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>Chaufferie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B10" s="31">
@@ -4039,7 +4475,7 @@
         <v/>
       </c>
       <c r="C10" s="32">
-        <f>'Récapitulatif 2025'!E16</f>
+        <f>'Récap Site 2025'!E13</f>
         <v/>
       </c>
       <c r="D10" s="32">
@@ -4058,7 +4494,7 @@
     <row r="11" ht="15.05" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Désenfumage</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B11" s="31">
@@ -4066,7 +4502,7 @@
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>'Récapitulatif 2025'!E19</f>
+        <f>'Récap Site 2025'!E16</f>
         <v/>
       </c>
       <c r="D11" s="32">
@@ -4085,7 +4521,7 @@
     <row r="12" ht="15.05" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Désenfumage</t>
         </is>
       </c>
       <c r="B12" s="31">
@@ -4093,7 +4529,7 @@
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>'Récapitulatif 2025'!E22</f>
+        <f>'Récap Site 2025'!E19</f>
         <v/>
       </c>
       <c r="D12" s="32">
@@ -4112,7 +4548,7 @@
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Espaces verts</t>
         </is>
       </c>
       <c r="B13" s="31">
@@ -4120,7 +4556,7 @@
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récapitulatif 2025'!E25</f>
+        <f>'Récap Site 2025'!E22</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -4139,7 +4575,7 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Portes Coupe-Feu</t>
         </is>
       </c>
       <c r="B14" s="31">
@@ -4147,7 +4583,7 @@
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récapitulatif 2025'!E28</f>
+        <f>'Récap Site 2025'!E25</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -4166,7 +4602,7 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Protection foudre</t>
         </is>
       </c>
       <c r="B15" s="31">
@@ -4174,7 +4610,7 @@
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récapitulatif 2025'!E31</f>
+        <f>'Récap Site 2025'!E28</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -4193,7 +4629,7 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B16" s="31">
@@ -4201,7 +4637,7 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récapitulatif 2025'!E37</f>
+        <f>'Récap Site 2025'!E31</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -4220,7 +4656,7 @@
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>Sprinklers - RIA - PI - Fioul</t>
         </is>
       </c>
       <c r="B17" s="31">
@@ -4228,7 +4664,7 @@
         <v/>
       </c>
       <c r="C17" s="32">
-        <f>'Récapitulatif 2025'!E40</f>
+        <f>'Récap Site 2025'!E37</f>
         <v/>
       </c>
       <c r="D17" s="32">
@@ -4247,7 +4683,7 @@
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B18" s="31">
@@ -4255,7 +4691,7 @@
         <v/>
       </c>
       <c r="C18" s="32">
-        <f>'Récapitulatif 2025'!E43</f>
+        <f>'Récap Site 2025'!E40</f>
         <v/>
       </c>
       <c r="D18" s="32">
@@ -4274,7 +4710,7 @@
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Toiture</t>
+          <t>Télésurveillance</t>
         </is>
       </c>
       <c r="B19" s="31">
@@ -4282,7 +4718,7 @@
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récapitulatif 2025'!E46</f>
+        <f>'Récap Site 2025'!E43</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -4298,64 +4734,64 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>'Récap Site 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sous-total — CONTRAT MAINTENANCE</t>
         </is>
       </c>
-      <c r="C20" s="8">
-        <f>SUM(C6:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>SUM(D6:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="8">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="8">
+        <f>SUM(C7:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>SUM(D7:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="8">
+        <f>SUM(F7:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>FLUIDES</t>
         </is>
-      </c>
-    </row>
-    <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C22" s="32">
-        <f>'Récapitulatif 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D22" s="32">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>Paramètres!$H$9/365</f>
-        <v/>
-      </c>
-      <c r="F22" s="32">
-        <f>D22*E22</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B23" s="31">
@@ -4363,7 +4799,7 @@
         <v/>
       </c>
       <c r="C23" s="32">
-        <f>'Récapitulatif 2025'!E63</f>
+        <f>'Récap Site 2025'!E60</f>
         <v/>
       </c>
       <c r="D23" s="32">
@@ -4382,7 +4818,7 @@
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B24" s="31">
@@ -4390,7 +4826,7 @@
         <v/>
       </c>
       <c r="C24" s="32">
-        <f>'Récapitulatif 2025'!E66</f>
+        <f>'Récap Site 2025'!E63</f>
         <v/>
       </c>
       <c r="D24" s="32">
@@ -4409,7 +4845,7 @@
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B25" s="31">
@@ -4417,7 +4853,7 @@
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récapitulatif 2025'!E69</f>
+        <f>'Récap Site 2025'!E66</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -4433,328 +4869,357 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="15.05" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C26" s="32">
+        <f>'Récap Site 2025'!E69</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="33">
+        <f>Paramètres!$H$9/365</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sous-total — FLUIDES</t>
         </is>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="8">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="8">
+        <f>SUM(C23:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="8">
+        <f>SUM(D23:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="8">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TAXES</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="29" ht="15.05" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Taxe Bureau &amp; Stationnement</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B29" s="31">
         <f>Paramètres!$C$9/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="32">
-        <f>'Récapitulatif 2025'!E73</f>
-        <v/>
-      </c>
-      <c r="D28" s="32">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="33">
+      <c r="C29" s="32">
+        <f>'Récap Site 2025'!E73</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="33">
         <f>Paramètres!$J$9/365</f>
         <v/>
       </c>
-      <c r="F28" s="32">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="F29" s="32">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TAXES</t>
         </is>
       </c>
-      <c r="C29" s="8">
-        <f>SUM(C28:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="8">
-        <f>SUM(D28:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="8">
-        <f>SUM(F28:F28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C30" s="8">
+        <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>SUM(D29:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="8">
+        <f>SUM(F29:F29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>HONORAIRES</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.05" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>Honoraires Divers</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B32" s="31">
         <f>Paramètres!$C$9/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C31" s="32">
-        <f>'Récapitulatif 2025'!E77</f>
-        <v/>
-      </c>
-      <c r="D31" s="32">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="33">
+      <c r="C32" s="32">
+        <f>'Récap Site 2025'!E77</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="33">
         <f>Paramètres!$J$9/365</f>
         <v/>
       </c>
-      <c r="F31" s="32">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="F32" s="32">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Sous-total — HONORAIRES</t>
         </is>
       </c>
-      <c r="C32" s="8">
-        <f>SUM(C31:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>SUM(D31:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="8">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C33" s="8">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="8">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TRAVAUX</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.05" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="35" ht="15.05" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>Paramètres!$C$9/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C34" s="32">
-        <f>'Récapitulatif 2025'!E81</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>B34*C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="33">
+      <c r="C35" s="32">
+        <f>'Récap Site 2025'!E81</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>B35*C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="33">
         <f>Paramètres!$J$9/365</f>
         <v/>
       </c>
-      <c r="F34" s="32">
-        <f>D34*E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F35" s="32">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TRAVAUX</t>
         </is>
       </c>
-      <c r="C35" s="8">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="8">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="8">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="7.55" customHeight="1"/>
-    <row r="37" ht="21.75" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="C36" s="8">
+        <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="8">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="7.55" customHeight="1"/>
+    <row r="39" ht="21.75" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C37" s="14">
-        <f>C20+C26+C29+C32+C35</f>
-        <v/>
-      </c>
-      <c r="D37" s="14">
-        <f>D20+D26+D29+D32+D35</f>
-        <v/>
-      </c>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="14">
-        <f>F20+F26+F29+F32+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="19.55" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="C39" s="14">
+        <f>C21+C27+C30+C33+C36</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>D21+D27+D30+D33+D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="14">
+        <f>F21+F27+F30+F33+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="7.55" customHeight="1"/>
+    <row r="41" ht="19.55" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.8" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.8" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.8" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.8" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.8" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.8" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D44" s="8">
-        <f>SUM(D40:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="8">
-        <f>SUM(F40:F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="7.55" customHeight="1"/>
-    <row r="46" ht="21.75" customHeight="1">
-      <c r="A46" s="37">
-        <f>IF(F37-F44&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D46" s="38">
-        <f>D37-D44</f>
-        <v/>
-      </c>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="38">
-        <f>F37-F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="D46" s="8">
+        <f>SUM(D42:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="8">
+        <f>SUM(F42:F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="7.55" customHeight="1"/>
+    <row r="48" ht="21.75" customHeight="1">
+      <c r="A48" s="37">
+        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D48" s="38">
+        <f>D39-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="38">
+        <f>F39-F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="27.75" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4797,7 +5262,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Total site HT</t>
+          <t>Total HT</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4816,44 +5281,24 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>CHARGES SITE — MEAUX PN01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CONTRAT MAINTENANCE</t>
         </is>
-      </c>
-    </row>
-    <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>Portails + Barrières automatiques</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>'Récapitulatif 2025'!E7</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>D6*E6</f>
-        <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B7" s="31">
@@ -4861,7 +5306,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récapitulatif 2025'!E34</f>
+        <f>'Récap Site 2025'!E7</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -4880,7 +5325,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Vérifications règlementaires</t>
+          <t>Séparateur hydro.</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -4888,7 +5333,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récapitulatif 2025'!E10</f>
+        <f>'Récap Site 2025'!E34</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -4907,7 +5352,7 @@
     <row r="9" ht="15.05" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Ascenseur</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B9" s="31">
@@ -4915,7 +5360,7 @@
         <v/>
       </c>
       <c r="C9" s="32">
-        <f>'Récapitulatif 2025'!E13</f>
+        <f>'Récap Site 2025'!E10</f>
         <v/>
       </c>
       <c r="D9" s="32">
@@ -4934,7 +5379,7 @@
     <row r="10" ht="15.05" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>Chaufferie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B10" s="31">
@@ -4942,7 +5387,7 @@
         <v/>
       </c>
       <c r="C10" s="32">
-        <f>'Récapitulatif 2025'!E16</f>
+        <f>'Récap Site 2025'!E13</f>
         <v/>
       </c>
       <c r="D10" s="32">
@@ -4961,7 +5406,7 @@
     <row r="11" ht="15.05" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Désenfumage</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B11" s="31">
@@ -4969,7 +5414,7 @@
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>'Récapitulatif 2025'!E19</f>
+        <f>'Récap Site 2025'!E16</f>
         <v/>
       </c>
       <c r="D11" s="32">
@@ -4988,7 +5433,7 @@
     <row r="12" ht="15.05" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Désenfumage</t>
         </is>
       </c>
       <c r="B12" s="31">
@@ -4996,7 +5441,7 @@
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>'Récapitulatif 2025'!E22</f>
+        <f>'Récap Site 2025'!E19</f>
         <v/>
       </c>
       <c r="D12" s="32">
@@ -5015,7 +5460,7 @@
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Espaces verts</t>
         </is>
       </c>
       <c r="B13" s="31">
@@ -5023,7 +5468,7 @@
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récapitulatif 2025'!E25</f>
+        <f>'Récap Site 2025'!E22</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -5042,7 +5487,7 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Portes Coupe-Feu</t>
         </is>
       </c>
       <c r="B14" s="31">
@@ -5050,7 +5495,7 @@
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récapitulatif 2025'!E28</f>
+        <f>'Récap Site 2025'!E25</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -5069,7 +5514,7 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Protection foudre</t>
         </is>
       </c>
       <c r="B15" s="31">
@@ -5077,7 +5522,7 @@
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récapitulatif 2025'!E31</f>
+        <f>'Récap Site 2025'!E28</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -5096,7 +5541,7 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B16" s="31">
@@ -5104,7 +5549,7 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récapitulatif 2025'!E37</f>
+        <f>'Récap Site 2025'!E31</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -5123,7 +5568,7 @@
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>Sprinklers - RIA - PI - Fioul</t>
         </is>
       </c>
       <c r="B17" s="31">
@@ -5131,7 +5576,7 @@
         <v/>
       </c>
       <c r="C17" s="32">
-        <f>'Récapitulatif 2025'!E40</f>
+        <f>'Récap Site 2025'!E37</f>
         <v/>
       </c>
       <c r="D17" s="32">
@@ -5150,7 +5595,7 @@
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B18" s="31">
@@ -5158,7 +5603,7 @@
         <v/>
       </c>
       <c r="C18" s="32">
-        <f>'Récapitulatif 2025'!E43</f>
+        <f>'Récap Site 2025'!E40</f>
         <v/>
       </c>
       <c r="D18" s="32">
@@ -5177,7 +5622,7 @@
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Toiture</t>
+          <t>Télésurveillance</t>
         </is>
       </c>
       <c r="B19" s="31">
@@ -5185,7 +5630,7 @@
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récapitulatif 2025'!E46</f>
+        <f>'Récap Site 2025'!E43</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -5201,64 +5646,64 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>'Récap Site 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sous-total — CONTRAT MAINTENANCE</t>
         </is>
       </c>
-      <c r="C20" s="8">
-        <f>SUM(C6:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>SUM(D6:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="8">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="8">
+        <f>SUM(C7:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>SUM(D7:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="8">
+        <f>SUM(F7:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>FLUIDES</t>
         </is>
-      </c>
-    </row>
-    <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C22" s="32">
-        <f>'Récapitulatif 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D22" s="32">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>Paramètres!$H$10/365</f>
-        <v/>
-      </c>
-      <c r="F22" s="32">
-        <f>D22*E22</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B23" s="31">
@@ -5266,7 +5711,7 @@
         <v/>
       </c>
       <c r="C23" s="32">
-        <f>'Récapitulatif 2025'!E63</f>
+        <f>'Récap Site 2025'!E60</f>
         <v/>
       </c>
       <c r="D23" s="32">
@@ -5285,7 +5730,7 @@
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B24" s="31">
@@ -5293,7 +5738,7 @@
         <v/>
       </c>
       <c r="C24" s="32">
-        <f>'Récapitulatif 2025'!E66</f>
+        <f>'Récap Site 2025'!E63</f>
         <v/>
       </c>
       <c r="D24" s="32">
@@ -5312,7 +5757,7 @@
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B25" s="31">
@@ -5320,7 +5765,7 @@
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récapitulatif 2025'!E69</f>
+        <f>'Récap Site 2025'!E66</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -5336,328 +5781,357 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="15.05" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C26" s="32">
+        <f>'Récap Site 2025'!E69</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="33">
+        <f>Paramètres!$H$10/365</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sous-total — FLUIDES</t>
         </is>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="8">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="8">
+        <f>SUM(C23:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="8">
+        <f>SUM(D23:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="8">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TAXES</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="29" ht="15.05" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Taxe Bureau &amp; Stationnement</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B29" s="31">
         <f>Paramètres!$C$10/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="32">
-        <f>'Récapitulatif 2025'!E73</f>
-        <v/>
-      </c>
-      <c r="D28" s="32">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="33">
+      <c r="C29" s="32">
+        <f>'Récap Site 2025'!E73</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="33">
         <f>Paramètres!$J$10/365</f>
         <v/>
       </c>
-      <c r="F28" s="32">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="F29" s="32">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TAXES</t>
         </is>
       </c>
-      <c r="C29" s="8">
-        <f>SUM(C28:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="8">
-        <f>SUM(D28:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="8">
-        <f>SUM(F28:F28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C30" s="8">
+        <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>SUM(D29:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="8">
+        <f>SUM(F29:F29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>HONORAIRES</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.05" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>Honoraires Divers</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B32" s="31">
         <f>Paramètres!$C$10/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C31" s="32">
-        <f>'Récapitulatif 2025'!E77</f>
-        <v/>
-      </c>
-      <c r="D31" s="32">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="33">
+      <c r="C32" s="32">
+        <f>'Récap Site 2025'!E77</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="33">
         <f>Paramètres!$J$10/365</f>
         <v/>
       </c>
-      <c r="F31" s="32">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="F32" s="32">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Sous-total — HONORAIRES</t>
         </is>
       </c>
-      <c r="C32" s="8">
-        <f>SUM(C31:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>SUM(D31:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="8">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C33" s="8">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="8">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TRAVAUX</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.05" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="35" ht="15.05" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>Paramètres!$C$10/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C34" s="32">
-        <f>'Récapitulatif 2025'!E81</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>B34*C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="33">
+      <c r="C35" s="32">
+        <f>'Récap Site 2025'!E81</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>B35*C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="33">
         <f>Paramètres!$J$10/365</f>
         <v/>
       </c>
-      <c r="F34" s="32">
-        <f>D34*E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F35" s="32">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TRAVAUX</t>
         </is>
       </c>
-      <c r="C35" s="8">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="8">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="8">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="7.55" customHeight="1"/>
-    <row r="37" ht="21.75" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="C36" s="8">
+        <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="8">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="7.55" customHeight="1"/>
+    <row r="39" ht="21.75" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C37" s="14">
-        <f>C20+C26+C29+C32+C35</f>
-        <v/>
-      </c>
-      <c r="D37" s="14">
-        <f>D20+D26+D29+D32+D35</f>
-        <v/>
-      </c>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="14">
-        <f>F20+F26+F29+F32+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="19.55" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="C39" s="14">
+        <f>C21+C27+C30+C33+C36</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>D21+D27+D30+D33+D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="14">
+        <f>F21+F27+F30+F33+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="7.55" customHeight="1"/>
+    <row r="41" ht="19.55" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.8" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.8" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.8" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.8" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.8" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.8" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D44" s="8">
-        <f>SUM(D40:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="8">
-        <f>SUM(F40:F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="7.55" customHeight="1"/>
-    <row r="46" ht="21.75" customHeight="1">
-      <c r="A46" s="37">
-        <f>IF(F37-F44&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D46" s="38">
-        <f>D37-D44</f>
-        <v/>
-      </c>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="38">
-        <f>F37-F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="D46" s="8">
+        <f>SUM(D42:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="8">
+        <f>SUM(F42:F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="7.55" customHeight="1"/>
+    <row r="48" ht="21.75" customHeight="1">
+      <c r="A48" s="37">
+        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D48" s="38">
+        <f>D39-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="38">
+        <f>F39-F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="27.75" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5700,7 +6174,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Total site HT</t>
+          <t>Total HT</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -5719,44 +6193,24 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>CHARGES SITE — MEAUX PN01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CONTRAT MAINTENANCE</t>
         </is>
-      </c>
-    </row>
-    <row r="6" ht="15.05" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>Portails + Barrières automatiques</t>
-        </is>
-      </c>
-      <c r="B6" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>'Récapitulatif 2025'!E7</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>D6*E6</f>
-        <v/>
       </c>
     </row>
     <row r="7" ht="15.05" customHeight="1">
       <c r="A7" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B7" s="31">
@@ -5764,7 +6218,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récapitulatif 2025'!E34</f>
+        <f>'Récap Site 2025'!E7</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -5783,7 +6237,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Vérifications règlementaires</t>
+          <t>Séparateur hydro.</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -5791,7 +6245,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récapitulatif 2025'!E10</f>
+        <f>'Récap Site 2025'!E34</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -5810,7 +6264,7 @@
     <row r="9" ht="15.05" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Ascenseur</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B9" s="31">
@@ -5818,7 +6272,7 @@
         <v/>
       </c>
       <c r="C9" s="32">
-        <f>'Récapitulatif 2025'!E13</f>
+        <f>'Récap Site 2025'!E10</f>
         <v/>
       </c>
       <c r="D9" s="32">
@@ -5837,7 +6291,7 @@
     <row r="10" ht="15.05" customHeight="1">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>Chaufferie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B10" s="31">
@@ -5845,7 +6299,7 @@
         <v/>
       </c>
       <c r="C10" s="32">
-        <f>'Récapitulatif 2025'!E16</f>
+        <f>'Récap Site 2025'!E13</f>
         <v/>
       </c>
       <c r="D10" s="32">
@@ -5864,7 +6318,7 @@
     <row r="11" ht="15.05" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
-          <t>Désenfumage</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B11" s="31">
@@ -5872,7 +6326,7 @@
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>'Récapitulatif 2025'!E19</f>
+        <f>'Récap Site 2025'!E16</f>
         <v/>
       </c>
       <c r="D11" s="32">
@@ -5891,7 +6345,7 @@
     <row r="12" ht="15.05" customHeight="1">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Désenfumage</t>
         </is>
       </c>
       <c r="B12" s="31">
@@ -5899,7 +6353,7 @@
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>'Récapitulatif 2025'!E22</f>
+        <f>'Récap Site 2025'!E19</f>
         <v/>
       </c>
       <c r="D12" s="32">
@@ -5918,7 +6372,7 @@
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Espaces verts</t>
         </is>
       </c>
       <c r="B13" s="31">
@@ -5926,7 +6380,7 @@
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récapitulatif 2025'!E25</f>
+        <f>'Récap Site 2025'!E22</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -5945,7 +6399,7 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Portes Coupe-Feu</t>
         </is>
       </c>
       <c r="B14" s="31">
@@ -5953,7 +6407,7 @@
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récapitulatif 2025'!E28</f>
+        <f>'Récap Site 2025'!E25</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -5972,7 +6426,7 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Protection foudre</t>
         </is>
       </c>
       <c r="B15" s="31">
@@ -5980,7 +6434,7 @@
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récapitulatif 2025'!E31</f>
+        <f>'Récap Site 2025'!E28</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -5999,7 +6453,7 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B16" s="31">
@@ -6007,7 +6461,7 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récapitulatif 2025'!E37</f>
+        <f>'Récap Site 2025'!E31</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -6026,7 +6480,7 @@
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>SSI</t>
+          <t>Sprinklers - RIA - PI - Fioul</t>
         </is>
       </c>
       <c r="B17" s="31">
@@ -6034,7 +6488,7 @@
         <v/>
       </c>
       <c r="C17" s="32">
-        <f>'Récapitulatif 2025'!E40</f>
+        <f>'Récap Site 2025'!E37</f>
         <v/>
       </c>
       <c r="D17" s="32">
@@ -6053,7 +6507,7 @@
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B18" s="31">
@@ -6061,7 +6515,7 @@
         <v/>
       </c>
       <c r="C18" s="32">
-        <f>'Récapitulatif 2025'!E43</f>
+        <f>'Récap Site 2025'!E40</f>
         <v/>
       </c>
       <c r="D18" s="32">
@@ -6080,7 +6534,7 @@
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Toiture</t>
+          <t>Télésurveillance</t>
         </is>
       </c>
       <c r="B19" s="31">
@@ -6088,7 +6542,7 @@
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récapitulatif 2025'!E46</f>
+        <f>'Récap Site 2025'!E43</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -6104,64 +6558,64 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="20" ht="15.05" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>'Récap Site 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sous-total — CONTRAT MAINTENANCE</t>
         </is>
       </c>
-      <c r="C20" s="8">
-        <f>SUM(C6:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8">
-        <f>SUM(D6:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="8">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="C21" s="8">
+        <f>SUM(C7:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8">
+        <f>SUM(D7:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="8">
+        <f>SUM(F7:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>FLUIDES</t>
         </is>
-      </c>
-    </row>
-    <row r="22" ht="15.05" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C22" s="32">
-        <f>'Récapitulatif 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D22" s="32">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="33">
-        <f>Paramètres!$H$11/365</f>
-        <v/>
-      </c>
-      <c r="F22" s="32">
-        <f>D22*E22</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>Eau</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B23" s="31">
@@ -6169,7 +6623,7 @@
         <v/>
       </c>
       <c r="C23" s="32">
-        <f>'Récapitulatif 2025'!E63</f>
+        <f>'Récap Site 2025'!E60</f>
         <v/>
       </c>
       <c r="D23" s="32">
@@ -6188,7 +6642,7 @@
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B24" s="31">
@@ -6196,7 +6650,7 @@
         <v/>
       </c>
       <c r="C24" s="32">
-        <f>'Récapitulatif 2025'!E66</f>
+        <f>'Récap Site 2025'!E63</f>
         <v/>
       </c>
       <c r="D24" s="32">
@@ -6215,7 +6669,7 @@
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B25" s="31">
@@ -6223,7 +6677,7 @@
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récapitulatif 2025'!E69</f>
+        <f>'Récap Site 2025'!E66</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -6239,596 +6693,345 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="15.05" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Gaz</t>
+        </is>
+      </c>
+      <c r="B26" s="31">
+        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <v/>
+      </c>
+      <c r="C26" s="32">
+        <f>'Récap Site 2025'!E69</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="33">
+        <f>Paramètres!$H$11/365</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sous-total — FLUIDES</t>
         </is>
       </c>
-      <c r="C26" s="8">
-        <f>SUM(C22:C25)</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>SUM(D22:D25)</f>
-        <v/>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="8">
-        <f>SUM(F22:F25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="8">
+        <f>SUM(C23:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="8">
+        <f>SUM(D23:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="8">
+        <f>SUM(F23:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>TAXES</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.05" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+    <row r="29" ht="15.05" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Taxe Bureau &amp; Stationnement</t>
         </is>
       </c>
-      <c r="B28" s="31">
+      <c r="B29" s="31">
         <f>Paramètres!$C$11/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C28" s="32">
-        <f>'Récapitulatif 2025'!E73</f>
-        <v/>
-      </c>
-      <c r="D28" s="32">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="33">
+      <c r="C29" s="32">
+        <f>'Récap Site 2025'!E73</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="33">
         <f>Paramètres!$J$11/365</f>
         <v/>
       </c>
-      <c r="F28" s="32">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="F29" s="32">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TAXES</t>
         </is>
       </c>
-      <c r="C29" s="8">
-        <f>SUM(C28:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="8">
-        <f>SUM(D28:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="8">
-        <f>SUM(F28:F28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="C30" s="8">
+        <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="8">
+        <f>SUM(D29:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="8">
+        <f>SUM(F29:F29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>HONORAIRES</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.05" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
+    <row r="32" ht="15.05" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>Honoraires Divers</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B32" s="31">
         <f>Paramètres!$C$11/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C31" s="32">
-        <f>'Récapitulatif 2025'!E77</f>
-        <v/>
-      </c>
-      <c r="D31" s="32">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="33">
+      <c r="C32" s="32">
+        <f>'Récap Site 2025'!E77</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="33">
         <f>Paramètres!$J$11/365</f>
         <v/>
       </c>
-      <c r="F31" s="32">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="F32" s="32">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Sous-total — HONORAIRES</t>
         </is>
       </c>
-      <c r="C32" s="8">
-        <f>SUM(C31:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="8">
-        <f>SUM(D31:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="8">
-        <f>SUM(F31:F31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C33" s="8">
+        <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="8">
+        <f>SUM(D32:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="8">
+        <f>SUM(F32:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TRAVAUX</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.05" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+    <row r="35" ht="15.05" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Entretien Courant</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>Paramètres!$C$11/Paramètres!$C$3</f>
         <v/>
       </c>
-      <c r="C34" s="32">
-        <f>'Récapitulatif 2025'!E81</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>B34*C34</f>
-        <v/>
-      </c>
-      <c r="E34" s="33">
+      <c r="C35" s="32">
+        <f>'Récap Site 2025'!E81</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>B35*C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="33">
         <f>Paramètres!$J$11/365</f>
         <v/>
       </c>
-      <c r="F34" s="32">
-        <f>D34*E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="F35" s="32">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Sous-total — TRAVAUX</t>
         </is>
       </c>
-      <c r="C35" s="8">
-        <f>SUM(C34:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="8">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="8">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="7.55" customHeight="1"/>
-    <row r="37" ht="21.75" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="C36" s="8">
+        <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="8">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="7.55" customHeight="1"/>
+    <row r="39" ht="21.75" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C37" s="14">
-        <f>C20+C26+C29+C32+C35</f>
-        <v/>
-      </c>
-      <c r="D37" s="14">
-        <f>D20+D26+D29+D32+D35</f>
-        <v/>
-      </c>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="14">
-        <f>F20+F26+F29+F32+F35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="19.55" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="C39" s="14">
+        <f>C21+C27+C30+C33+C36</f>
+        <v/>
+      </c>
+      <c r="D39" s="14">
+        <f>D21+D27+D30+D33+D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="14">
+        <f>F21+F27+F30+F33+F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="7.55" customHeight="1"/>
+    <row r="41" ht="19.55" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n"/>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.8" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15.8" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.8" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.8" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.8" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15.8" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D44" s="8">
-        <f>SUM(D40:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="8">
-        <f>SUM(F40:F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="7.55" customHeight="1"/>
-    <row r="46" ht="21.75" customHeight="1">
-      <c r="A46" s="37">
-        <f>IF(F37-F44&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D46" s="38">
-        <f>D37-D44</f>
-        <v/>
-      </c>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="38">
-        <f>F37-F44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="D46" s="8">
+        <f>SUM(D42:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="8">
+        <f>SUM(F42:F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="7.55" customHeight="1"/>
+    <row r="48" ht="21.75" customHeight="1">
+      <c r="A48" s="37">
+        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D48" s="38">
+        <f>D39-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="38">
+        <f>F39-F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="27.75" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A35:B35"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.55" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>MEAUX PN01 — COÛT DE LA VACANCE LOCATIVE 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.8" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Estimation de la perte de charges non récupérées sur les lots vacants</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Statut</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Surface (m²)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>QP annuelle (€ HT)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Période (j/365)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Coût vacance (€ HT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="40">
-        <f>Paramètres!A7</f>
-        <v/>
-      </c>
-      <c r="B5" s="18">
-        <f>Paramètres!B7</f>
-        <v/>
-      </c>
-      <c r="C5" s="41">
-        <f>Paramètres!C7</f>
-        <v/>
-      </c>
-      <c r="D5" s="32">
-        <f>'BAT 1 - MEAUX I'!D37</f>
-        <v/>
-      </c>
-      <c r="E5" s="33">
-        <f>Paramètres!H7/365</f>
-        <v/>
-      </c>
-      <c r="F5" s="28">
-        <f>IF(Paramètres!B7="Vacant",'BAT 1 - MEAUX I'!D37,'BAT 1 - MEAUX I'!D37-'BAT 1 - MEAUX I'!F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="40">
-        <f>Paramètres!A8</f>
-        <v/>
-      </c>
-      <c r="B6" s="18">
-        <f>Paramètres!B8</f>
-        <v/>
-      </c>
-      <c r="C6" s="41">
-        <f>Paramètres!C8</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>'C1'!D37</f>
-        <v/>
-      </c>
-      <c r="E6" s="33">
-        <f>Paramètres!H8/365</f>
-        <v/>
-      </c>
-      <c r="F6" s="28">
-        <f>IF(Paramètres!B8="Vacant",'C1'!D37,'C1'!D37-'C1'!F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="40">
-        <f>Paramètres!A9</f>
-        <v/>
-      </c>
-      <c r="B7" s="18">
-        <f>Paramètres!B9</f>
-        <v/>
-      </c>
-      <c r="C7" s="41">
-        <f>Paramètres!C9</f>
-        <v/>
-      </c>
-      <c r="D7" s="32">
-        <f>'C2'!D37</f>
-        <v/>
-      </c>
-      <c r="E7" s="33">
-        <f>Paramètres!H9/365</f>
-        <v/>
-      </c>
-      <c r="F7" s="28">
-        <f>IF(Paramètres!B9="Vacant",'C2'!D37,'C2'!D37-'C2'!F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="40">
-        <f>Paramètres!A10</f>
-        <v/>
-      </c>
-      <c r="B8" s="18">
-        <f>Paramètres!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="41">
-        <f>Paramètres!C10</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
-        <f>'C3'!D37</f>
-        <v/>
-      </c>
-      <c r="E8" s="33">
-        <f>Paramètres!H10/365</f>
-        <v/>
-      </c>
-      <c r="F8" s="28">
-        <f>IF(Paramètres!B10="Vacant",'C3'!D37,'C3'!D37-'C3'!F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="40">
-        <f>Paramètres!A11</f>
-        <v/>
-      </c>
-      <c r="B9" s="18">
-        <f>Paramètres!B11</f>
-        <v/>
-      </c>
-      <c r="C9" s="41">
-        <f>Paramètres!C11</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>'C4'!D37</f>
-        <v/>
-      </c>
-      <c r="E9" s="33">
-        <f>Paramètres!H11/365</f>
-        <v/>
-      </c>
-      <c r="F9" s="28">
-        <f>IF(Paramètres!B11="Vacant",'C4'!D37,'C4'!D37-'C4'!F37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Total QP charges (tous lots)</t>
-        </is>
-      </c>
-      <c r="D11" s="8">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E11" s="34" t="n"/>
-      <c r="F11" s="34" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Nombre de lots vacants</t>
-        </is>
-      </c>
-      <c r="D12" s="42">
-        <f>COUNTIF(B5:B9,"Vacant")</f>
-        <v/>
-      </c>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="34" t="n"/>
-    </row>
-    <row r="13" ht="6" customHeight="1"/>
-    <row r="14" ht="19.55" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Charges non récupérables (Frais Bancaires + CAPEX)</t>
-        </is>
-      </c>
-      <c r="F14" s="44">
-        <f>'Récapitulatif 2025'!E50+'Récapitulatif 2025'!E53+'Récapitulatif 2025'!E56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="25.55" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>TOTAL COÛT DE LA VACANCE LOCATIVE (€ HT)</t>
-        </is>
-      </c>
-      <c r="F16" s="46">
-        <f>F5+F6+F7+F8+F9+F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="19.55" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Part vacance sur total charges site</t>
-        </is>
-      </c>
-      <c r="F18" s="47">
-        <f>IF(D11&gt;0,F16/D11,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="27.75" customHeight="1">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>ℹ  QP annuelle = Total site HT × clé de répartition. Coût vacance = QP annuelle × fraction de l'année non occupée.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/regularisation_MEAUX_PN01_2025.xlsx
+++ b/regularisation_MEAUX_PN01_2025.xlsx
@@ -76,14 +76,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -174,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,22 +200,22 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,16 +224,16 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -266,22 +266,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -290,7 +296,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -676,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -767,7 +773,7 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2544.41</v>
+        <v>550.66</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -791,655 +797,75 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>8575</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ascenseur</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="D12" s="6" t="inlineStr">
+        <v>4395</v>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>── CHARGES NON RECUPERABLES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Frais Bancaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>— Aucune facture —</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Ascenseur</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>131.67</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Chaufferie</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="13.5" customHeight="1">
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.8" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Chaufferie</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>4977.6</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Désenfumage</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.8" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Désenfumage</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>3978</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Espaces verts</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.8" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Espaces verts</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>11681.28</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Portes Coupe-Feu</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15.8" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Portes Coupe-Feu</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>2068.74</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Protection foudre</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.8" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Protection foudre</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Quais &amp; Portes sectionnelles</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.8" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Quais &amp; Portes sectionnelles</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>5397</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Séparateur hydro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15.8" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Séparateur hydro.</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>3536.4</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15.8" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>29712.56</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15.8" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — SSI</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>3455.06</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Télésurveillance</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15.8" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Télésurveillance</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>21381.7</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Toiture</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15.8" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Toiture</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>13339.98</v>
-      </c>
-    </row>
-    <row r="47" ht="21.75" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>── CHARGES NON RECUPERABLES ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Frais Bancaires</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15.8" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="14" ht="15.8" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    Sous-total — Frais Bancaires</t>
         </is>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <v>28.97</v>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Entretien Courant</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15.8" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Entretien Courant</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>40526.16</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Honoraires Huissiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="15.05" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>260858.01</v>
-      </c>
-      <c r="C55" s="9" t="inlineStr"/>
-      <c r="D55" s="9" t="inlineStr"/>
-      <c r="E55" s="11" t="n">
-        <v>355817.63</v>
-      </c>
-      <c r="F55" s="11" t="n">
-        <v>355817.63</v>
-      </c>
-      <c r="G55" s="11" t="n">
-        <v>46865.48</v>
-      </c>
-    </row>
-    <row r="56" ht="15.8" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Honoraires Huissiers</t>
-        </is>
-      </c>
-      <c r="E56" s="8">
-        <f>SUM(E55:E55)</f>
-        <v/>
-      </c>
-      <c r="F56" s="8">
-        <f>SUM(F55:F55)</f>
-        <v/>
-      </c>
-      <c r="G56" s="8">
-        <f>SUM(G55:G55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="21.75" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>── FLUIDES ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Electricité</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="15.8" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Electricité</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>48197.11</v>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Eau</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15.8" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Eau</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>8091.23</v>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Eau - Incendie</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15.8" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Eau - Incendie</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>2472.06</v>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15.8" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Gaz</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>5477.910000000001</v>
-      </c>
-    </row>
-    <row r="70" ht="21.75" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>── TAXES ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Taxe Bureau &amp; Stationnement</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="13.5" customHeight="1">
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15.8" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Taxe Bureau &amp; Stationnement</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>112446</v>
-      </c>
-    </row>
-    <row r="74" ht="21.75" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>── HONORAIRES ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Honoraires Divers</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15.8" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Honoraires Divers</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="78" ht="21.75" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>── TRAVAUX ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Entretien Courant</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="13.5" customHeight="1">
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>— Aucune facture —</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15.8" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Sous-total — Entretien Courant</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>23248.79</v>
-      </c>
-    </row>
-    <row r="82" ht="6" customHeight="1"/>
-    <row r="83" ht="19.55" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="19.55" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TOTAL — CHARGES NON RÉCUPÉRABLES</t>
         </is>
       </c>
-      <c r="E83" s="12">
-        <f>E50+E53+E56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="6" customHeight="1"/>
-    <row r="85" ht="25.55" customHeight="1">
-      <c r="A85" s="13" t="inlineStr">
+      <c r="E16" s="9">
+        <f>E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="25.55" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>TOTAL GÉNÉRAL — CHARGES RÉCUPÉRABLES</t>
         </is>
       </c>
-      <c r="E85" s="14">
-        <f>E7+E10+E13+E16+E19+E22+E25+E28+E31+E34+E37+E40+E43+E46+E60+E63+E66+E69+E73+E77+E81</f>
+      <c r="E18" s="11">
+        <f>E7+E10</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A53:D53"/>
+  <mergeCells count="9">
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A83:D83"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A85:D85"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1510,7 +936,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="40">
+      <c r="A5" s="42">
         <f>Paramètres!A7</f>
         <v/>
       </c>
@@ -1518,12 +944,12 @@
         <f>Paramètres!B7</f>
         <v/>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="43">
         <f>Paramètres!C7</f>
         <v/>
       </c>
       <c r="D5" s="32">
-        <f>'BAT 1 - MEAUX I'!D39</f>
+        <f>'BAT 1 - MEAUX I'!D27</f>
         <v/>
       </c>
       <c r="E5" s="33">
@@ -1531,12 +957,12 @@
         <v/>
       </c>
       <c r="F5" s="28">
-        <f>IF(Paramètres!B7="Vacant",'BAT 1 - MEAUX I'!D39,'BAT 1 - MEAUX I'!D39-'BAT 1 - MEAUX I'!F39)</f>
+        <f>IF(Paramètres!B7="Vacant",'BAT 1 - MEAUX I'!D27,'BAT 1 - MEAUX I'!D27-'BAT 1 - MEAUX I'!F27)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="40">
+      <c r="A6" s="42">
         <f>Paramètres!A8</f>
         <v/>
       </c>
@@ -1544,12 +970,12 @@
         <f>Paramètres!B8</f>
         <v/>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="43">
         <f>Paramètres!C8</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>'C1'!D39</f>
+        <f>'C1'!D45</f>
         <v/>
       </c>
       <c r="E6" s="33">
@@ -1557,12 +983,12 @@
         <v/>
       </c>
       <c r="F6" s="28">
-        <f>IF(Paramètres!B8="Vacant",'C1'!D39,'C1'!D39-'C1'!F39)</f>
+        <f>IF(Paramètres!B8="Vacant",'C1'!D45,'C1'!D45-'C1'!F45)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="40">
+      <c r="A7" s="42">
         <f>Paramètres!A9</f>
         <v/>
       </c>
@@ -1570,12 +996,12 @@
         <f>Paramètres!B9</f>
         <v/>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="43">
         <f>Paramètres!C9</f>
         <v/>
       </c>
       <c r="D7" s="32">
-        <f>'C2'!D39</f>
+        <f>'C2'!D45</f>
         <v/>
       </c>
       <c r="E7" s="33">
@@ -1583,12 +1009,12 @@
         <v/>
       </c>
       <c r="F7" s="28">
-        <f>IF(Paramètres!B9="Vacant",'C2'!D39,'C2'!D39-'C2'!F39)</f>
+        <f>IF(Paramètres!B9="Vacant",'C2'!D45,'C2'!D45-'C2'!F45)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="40">
+      <c r="A8" s="42">
         <f>Paramètres!A10</f>
         <v/>
       </c>
@@ -1596,12 +1022,12 @@
         <f>Paramètres!B10</f>
         <v/>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="43">
         <f>Paramètres!C10</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>'C3'!D39</f>
+        <f>'C3'!D45</f>
         <v/>
       </c>
       <c r="E8" s="33">
@@ -1609,12 +1035,12 @@
         <v/>
       </c>
       <c r="F8" s="28">
-        <f>IF(Paramètres!B10="Vacant",'C3'!D39,'C3'!D39-'C3'!F39)</f>
+        <f>IF(Paramètres!B10="Vacant",'C3'!D45,'C3'!D45-'C3'!F45)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="40">
+      <c r="A9" s="42">
         <f>Paramètres!A11</f>
         <v/>
       </c>
@@ -1622,12 +1048,12 @@
         <f>Paramètres!B11</f>
         <v/>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="43">
         <f>Paramètres!C11</f>
         <v/>
       </c>
       <c r="D9" s="32">
-        <f>'C4'!D39</f>
+        <f>'C4'!D45</f>
         <v/>
       </c>
       <c r="E9" s="33">
@@ -1635,7 +1061,7 @@
         <v/>
       </c>
       <c r="F9" s="28">
-        <f>IF(Paramètres!B11="Vacant",'C4'!D39,'C4'!D39-'C4'!F39)</f>
+        <f>IF(Paramètres!B11="Vacant",'C4'!D45,'C4'!D45-'C4'!F45)</f>
         <v/>
       </c>
     </row>
@@ -1659,7 +1085,7 @@
           <t>Nombre de lots vacants</t>
         </is>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="44">
         <f>COUNTIF(B5:B9,"Vacant")</f>
         <v/>
       </c>
@@ -1668,24 +1094,24 @@
     </row>
     <row r="13" ht="6" customHeight="1"/>
     <row r="14" ht="19.55" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>Charges non récupérables (Frais Bancaires + CAPEX)</t>
         </is>
       </c>
-      <c r="F14" s="44">
-        <f>'Récap Site 2025'!E50+'Récap Site 2025'!E53+'Récap Site 2025'!E56</f>
+      <c r="F14" s="46">
+        <f>'Récap Site 2025'!E14</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16" ht="25.55" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>TOTAL COÛT DE LA VACANCE LOCATIVE (€ HT)</t>
         </is>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="48">
         <f>F5+F6+F7+F8+F9+F14</f>
         <v/>
       </c>
@@ -1697,14 +1123,14 @@
           <t>Part vacance sur total charges site</t>
         </is>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="49">
         <f>IF(D11&gt;0,F16/D11,0)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="6" customHeight="1"/>
     <row r="20" ht="27.75" customHeight="1">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>ℹ  QP annuelle = Total site HT × clé de répartition. Coût vacance = QP annuelle × fraction de l'année non occupée.</t>
         </is>
@@ -1731,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1794,10 +1220,168 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="21.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>── FLUIDES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Electricité</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.8" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Electricité</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1974.51</v>
+      </c>
+    </row>
+    <row r="8" ht="21.75" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>── CONTRAT MAINTENANCE ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vérifications règlementaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.8" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" ht="21.75" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>── TAXES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.8" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>51423</v>
+      </c>
+    </row>
+    <row r="16" ht="21.75" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>── CHARGES NON RECUPERABLES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Entretien Courant</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.8" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Entretien Courant</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>7115</v>
+      </c>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="19.55" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL — CHARGES NON RÉCUPÉRABLES</t>
+        </is>
+      </c>
+      <c r="E21" s="9">
+        <f>E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="25.55" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL GÉNÉRAL — CHARGES RÉCUPÉRABLES</t>
+        </is>
+      </c>
+      <c r="E23" s="11">
+        <f>E7+E11+E15</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="12">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1809,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1872,10 +1456,682 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="21.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>── FLUIDES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Eau</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.8" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Eau</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>8091.23</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Eau - Incendie</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.8" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Eau - Incendie</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>2472.06</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Electricité</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.8" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Electricité</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>46222.6</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.8" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Gaz</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>5477.910000000001</v>
+      </c>
+    </row>
+    <row r="17" ht="21.75" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>── HONORAIRES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Honoraires Divers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.8" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Honoraires Divers</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="21" ht="21.75" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>── TRAVAUX ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Entretien Courant</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.8" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Entretien Courant</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>23248.79</v>
+      </c>
+    </row>
+    <row r="25" ht="21.75" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>── CONTRAT MAINTENANCE ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ascenseur</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.8" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Ascenseur</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>131.67</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Chaufferie</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.8" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Chaufferie</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>4977.6</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Désenfumage</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="13.5" customHeight="1">
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.8" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Désenfumage</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Espaces verts</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="13.5" customHeight="1">
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15.8" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Espaces verts</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>11681.28</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Portails + Barrières automatiques</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="13.5" customHeight="1">
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15.8" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Portails + Barrières automatiques</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1993.75</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Portes Coupe-Feu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="13.5" customHeight="1">
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15.8" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Portes Coupe-Feu</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>2068.74</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Protection foudre</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="13.5" customHeight="1">
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15.8" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Protection foudre</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Quais &amp; Portes sectionnelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="13.5" customHeight="1">
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.8" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Quais &amp; Portes sectionnelles</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>5397</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Séparateur hydro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="13.5" customHeight="1">
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15.8" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Séparateur hydro.</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>3536.4</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sprinklers - RIA - PI - Fioul</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="13.5" customHeight="1">
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15.8" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Sprinklers - RIA - PI - Fioul</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>29712.56</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="13.5" customHeight="1">
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15.8" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — SSI</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>3455.06</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Télésurveillance</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="13.5" customHeight="1">
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15.8" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Télésurveillance</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>21381.7</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Toiture</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="13.5" customHeight="1">
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.8" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Toiture</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>13339.98</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vérifications règlementaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="13.5" customHeight="1">
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.8" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="68" ht="21.75" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>── TAXES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="13.5" customHeight="1">
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15.8" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>61023</v>
+      </c>
+    </row>
+    <row r="72" ht="21.75" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>── CHARGES NON RECUPERABLES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Entretien Courant</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="13.5" customHeight="1">
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>— Aucune facture —</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15.8" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Entretien Courant</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>33411.16</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Honoraires Huissiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15.05" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="n">
+        <v>260858.01</v>
+      </c>
+      <c r="C77" s="12" t="inlineStr"/>
+      <c r="D77" s="12" t="inlineStr"/>
+      <c r="E77" s="14" t="n">
+        <v>355817.63</v>
+      </c>
+      <c r="F77" s="14" t="n">
+        <v>355817.63</v>
+      </c>
+      <c r="G77" s="14" t="n">
+        <v>46865.48</v>
+      </c>
+    </row>
+    <row r="78" ht="15.8" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Honoraires Huissiers</t>
+        </is>
+      </c>
+      <c r="E78" s="8">
+        <f>SUM(E77:E77)</f>
+        <v/>
+      </c>
+      <c r="F78" s="8">
+        <f>SUM(F77:F77)</f>
+        <v/>
+      </c>
+      <c r="G78" s="8">
+        <f>SUM(G77:G77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="6" customHeight="1"/>
+    <row r="80" ht="19.55" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL — CHARGES NON RÉCUPÉRABLES</t>
+        </is>
+      </c>
+      <c r="E80" s="9">
+        <f>E75+E78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="6" customHeight="1"/>
+    <row r="82" ht="25.55" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL GÉNÉRAL — CHARGES RÉCUPÉRABLES</t>
+        </is>
+      </c>
+      <c r="E82" s="11">
+        <f>E7+E10+E13+E16+E20+E24+E28+E31+E34+E37+E40+E43+E46+E49+E52+E55+E58+E61+E64+E67+E71</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="33">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2230,241 +2486,241 @@
     </row>
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A7,FIND(" — ",'Récap Site 2025'!A7)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A40,FIND(" — ",'Récap MEAUX II 2025'!A40)+4,100),"")</f>
         <v/>
       </c>
       <c r="C14" s="28">
-        <f>'Récap Site 2025'!E7</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A10,FIND(" — ",'Récap Site 2025'!A10)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A67,FIND(" — ",'Récap MEAUX II 2025'!A67)+4,100),"")</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>'Récap Site 2025'!E10</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A13,FIND(" — ",'Récap Site 2025'!A13)+4,100),"")</f>
+        <f>IFERROR(MID('Récap Site 2025'!A14,FIND(" — ",'Récap Site 2025'!A14)+4,100),"")</f>
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>'Récap Site 2025'!E13</f>
+        <f>'Récap Site 2025'!E14</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15.05" customHeight="1">
       <c r="A17" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A16,FIND(" — ",'Récap Site 2025'!A16)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A13,FIND(" — ",'Récap MEAUX II 2025'!A13)+4,100),"")</f>
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>'Récap Site 2025'!E16</f>
+        <f>'Récap MEAUX II 2025'!E13</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15.05" customHeight="1">
       <c r="A18" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A19,FIND(" — ",'Récap Site 2025'!A19)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A71,FIND(" — ",'Récap MEAUX II 2025'!A71)+4,100),"")</f>
         <v/>
       </c>
       <c r="C18" s="28">
-        <f>'Récap Site 2025'!E19</f>
+        <f>'Récap MEAUX II 2025'!E71</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A22,FIND(" — ",'Récap Site 2025'!A22)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A75,FIND(" — ",'Récap MEAUX II 2025'!A75)+4,100),"")</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>'Récap Site 2025'!E22</f>
+        <f>'Récap MEAUX II 2025'!E75</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15.05" customHeight="1">
       <c r="A20" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A25,FIND(" — ",'Récap Site 2025'!A25)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A7,FIND(" — ",'Récap MEAUX II 2025'!A7)+4,100),"")</f>
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>'Récap Site 2025'!E25</f>
+        <f>'Récap MEAUX II 2025'!E7</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15.05" customHeight="1">
       <c r="A21" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A28,FIND(" — ",'Récap Site 2025'!A28)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A10,FIND(" — ",'Récap MEAUX II 2025'!A10)+4,100),"")</f>
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>'Récap Site 2025'!E28</f>
+        <f>'Récap MEAUX II 2025'!E10</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15.05" customHeight="1">
       <c r="A22" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A31,FIND(" — ",'Récap Site 2025'!A31)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A16,FIND(" — ",'Récap MEAUX II 2025'!A16)+4,100),"")</f>
         <v/>
       </c>
       <c r="C22" s="28">
-        <f>'Récap Site 2025'!E31</f>
+        <f>'Récap MEAUX II 2025'!E16</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15.05" customHeight="1">
       <c r="A23" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A34,FIND(" — ",'Récap Site 2025'!A34)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A20,FIND(" — ",'Récap MEAUX II 2025'!A20)+4,100),"")</f>
         <v/>
       </c>
       <c r="C23" s="28">
-        <f>'Récap Site 2025'!E34</f>
+        <f>'Récap MEAUX II 2025'!E20</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A37,FIND(" — ",'Récap Site 2025'!A37)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A24,FIND(" — ",'Récap MEAUX II 2025'!A24)+4,100),"")</f>
         <v/>
       </c>
       <c r="C24" s="28">
-        <f>'Récap Site 2025'!E37</f>
+        <f>'Récap MEAUX II 2025'!E24</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A40,FIND(" — ",'Récap Site 2025'!A40)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A28,FIND(" — ",'Récap MEAUX II 2025'!A28)+4,100),"")</f>
         <v/>
       </c>
       <c r="C25" s="28">
-        <f>'Récap Site 2025'!E40</f>
+        <f>'Récap MEAUX II 2025'!E28</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15.05" customHeight="1">
       <c r="A26" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A43,FIND(" — ",'Récap Site 2025'!A43)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A31,FIND(" — ",'Récap MEAUX II 2025'!A31)+4,100),"")</f>
         <v/>
       </c>
       <c r="C26" s="28">
-        <f>'Récap Site 2025'!E43</f>
+        <f>'Récap MEAUX II 2025'!E31</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15.05" customHeight="1">
       <c r="A27" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A46,FIND(" — ",'Récap Site 2025'!A46)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A34,FIND(" — ",'Récap MEAUX II 2025'!A34)+4,100),"")</f>
         <v/>
       </c>
       <c r="C27" s="28">
-        <f>'Récap Site 2025'!E46</f>
+        <f>'Récap MEAUX II 2025'!E34</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15.05" customHeight="1">
       <c r="A28" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A50,FIND(" — ",'Récap Site 2025'!A50)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A37,FIND(" — ",'Récap MEAUX II 2025'!A37)+4,100),"")</f>
         <v/>
       </c>
       <c r="C28" s="28">
-        <f>'Récap Site 2025'!E50</f>
+        <f>'Récap MEAUX II 2025'!E37</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
       <c r="A29" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A53,FIND(" — ",'Récap Site 2025'!A53)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A43,FIND(" — ",'Récap MEAUX II 2025'!A43)+4,100),"")</f>
         <v/>
       </c>
       <c r="C29" s="28">
-        <f>'Récap Site 2025'!E53</f>
+        <f>'Récap MEAUX II 2025'!E43</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15.05" customHeight="1">
       <c r="A30" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A56,FIND(" — ",'Récap Site 2025'!A56)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A46,FIND(" — ",'Récap MEAUX II 2025'!A46)+4,100),"")</f>
         <v/>
       </c>
       <c r="C30" s="28">
-        <f>'Récap Site 2025'!E56</f>
+        <f>'Récap MEAUX II 2025'!E46</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15.05" customHeight="1">
       <c r="A31" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A60,FIND(" — ",'Récap Site 2025'!A60)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A49,FIND(" — ",'Récap MEAUX II 2025'!A49)+4,100),"")</f>
         <v/>
       </c>
       <c r="C31" s="28">
-        <f>'Récap Site 2025'!E60</f>
+        <f>'Récap MEAUX II 2025'!E49</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15.05" customHeight="1">
       <c r="A32" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A63,FIND(" — ",'Récap Site 2025'!A63)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A52,FIND(" — ",'Récap MEAUX II 2025'!A52)+4,100),"")</f>
         <v/>
       </c>
       <c r="C32" s="28">
-        <f>'Récap Site 2025'!E63</f>
+        <f>'Récap MEAUX II 2025'!E52</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15.05" customHeight="1">
       <c r="A33" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A66,FIND(" — ",'Récap Site 2025'!A66)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A55,FIND(" — ",'Récap MEAUX II 2025'!A55)+4,100),"")</f>
         <v/>
       </c>
       <c r="C33" s="28">
-        <f>'Récap Site 2025'!E66</f>
+        <f>'Récap MEAUX II 2025'!E55</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15.05" customHeight="1">
       <c r="A34" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A69,FIND(" — ",'Récap Site 2025'!A69)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A58,FIND(" — ",'Récap MEAUX II 2025'!A58)+4,100),"")</f>
         <v/>
       </c>
       <c r="C34" s="28">
-        <f>'Récap Site 2025'!E69</f>
+        <f>'Récap MEAUX II 2025'!E58</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
       <c r="A35" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A73,FIND(" — ",'Récap Site 2025'!A73)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A61,FIND(" — ",'Récap MEAUX II 2025'!A61)+4,100),"")</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>'Récap Site 2025'!E73</f>
+        <f>'Récap MEAUX II 2025'!E61</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15.05" customHeight="1">
       <c r="A36" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A77,FIND(" — ",'Récap Site 2025'!A77)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A64,FIND(" — ",'Récap MEAUX II 2025'!A64)+4,100),"")</f>
         <v/>
       </c>
       <c r="C36" s="28">
-        <f>'Récap Site 2025'!E77</f>
+        <f>'Récap MEAUX II 2025'!E64</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15.05" customHeight="1">
       <c r="A37" s="27">
-        <f>IFERROR(MID('Récap Site 2025'!A81,FIND(" — ",'Récap Site 2025'!A81)+4,100),"")</f>
+        <f>IFERROR(MID('Récap MEAUX II 2025'!A78,FIND(" — ",'Récap MEAUX II 2025'!A78)+4,100),"")</f>
         <v/>
       </c>
       <c r="C37" s="28">
-        <f>'Récap Site 2025'!E81</f>
+        <f>'Récap MEAUX II 2025'!E78</f>
         <v/>
       </c>
     </row>
@@ -2483,7 +2739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2546,7 +2802,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>CHARGES SITE — MEAUX PN01</t>
         </is>
@@ -2570,7 +2826,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récap Site 2025'!E7</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -2589,7 +2845,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -2597,7 +2853,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récap Site 2025'!E34</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -2613,126 +2869,53 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.05" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Vérifications règlementaires</t>
-        </is>
-      </c>
-      <c r="B9" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>'Récap Site 2025'!E10</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>Ascenseur</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>'Récap Site 2025'!E13</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>Chaufferie</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>'Récap Site 2025'!E16</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>Désenfumage</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>'Récap Site 2025'!E19</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>D12*E12</f>
-        <v/>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D7:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="8">
+        <f>SUM(F7:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CHARGES BÂTIMENT — MEAUX I</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>FLUIDES</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B13" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <f>Paramètres!$C$7/32653.4</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récap Site 2025'!E22</f>
+        <f>'Récap MEAUX II 2025'!E13</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -2740,7 +2923,7 @@
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>Paramètres!$J$7/365</f>
+        <f>Paramètres!$H$7/365</f>
         <v/>
       </c>
       <c r="F13" s="32">
@@ -2748,72 +2931,45 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="15.05" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>Portes Coupe-Feu</t>
-        </is>
-      </c>
-      <c r="B14" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C14" s="32">
-        <f>'Récap Site 2025'!E25</f>
-        <v/>
-      </c>
-      <c r="D14" s="32">
-        <f>B14*C14</f>
-        <v/>
-      </c>
-      <c r="E14" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F14" s="32">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15.05" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>Protection foudre</t>
-        </is>
-      </c>
-      <c r="B15" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C15" s="32">
-        <f>'Récap Site 2025'!E28</f>
-        <v/>
-      </c>
-      <c r="D15" s="32">
-        <f>B15*C15</f>
-        <v/>
-      </c>
-      <c r="E15" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F15" s="32">
-        <f>D15*E15</f>
-        <v/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C14" s="8">
+        <f>SUM(C13:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="8">
+        <f>SUM(D13:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="8">
+        <f>SUM(F13:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>CONTRAT MAINTENANCE</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B16" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <f>Paramètres!$C$7/32653.4</f>
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récap Site 2025'!E31</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -2829,72 +2985,45 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-      <c r="B17" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>'Récap Site 2025'!E37</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>'Récap Site 2025'!E40</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>D18*E18</f>
-        <v/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>SUM(C16:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>SUM(D16:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="8">
+        <f>SUM(F16:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>TAXES</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>Taxe Bureau &amp; Stationnement</t>
         </is>
       </c>
       <c r="B19" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
+        <f>Paramètres!$C$7/32653.4</f>
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récap Site 2025'!E43</f>
+        <f>'Récap MEAUX II 2025'!E71</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -2910,480 +3039,200 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Toiture</t>
-        </is>
-      </c>
-      <c r="B20" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C20" s="32">
-        <f>'Récap Site 2025'!E46</f>
-        <v/>
-      </c>
-      <c r="D20" s="32">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F20" s="32">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — CONTRAT MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>SUM(C7:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8">
-        <f>SUM(D7:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="8">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FLUIDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B23" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C23" s="32">
-        <f>'Récap Site 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D23" s="32">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="33">
-        <f>Paramètres!$H$7/365</f>
-        <v/>
-      </c>
-      <c r="F23" s="32">
-        <f>D23*E23</f>
-        <v/>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TAXES</t>
+        </is>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>SUM(D19:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="8">
+        <f>SUM(F19:F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="15.05" customHeight="1">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>Eau</t>
-        </is>
-      </c>
-      <c r="B24" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C24" s="32">
-        <f>'Récap Site 2025'!E63</f>
-        <v/>
-      </c>
-      <c r="D24" s="32">
-        <f>B24*C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="33">
-        <f>Paramètres!$H$7/365</f>
-        <v/>
+          <t>Honoraires Gestion Technique</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="36" t="n">
+        <v>1</v>
       </c>
       <c r="F24" s="32">
-        <f>D24*E24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15.05" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>Eau - Incendie</t>
-        </is>
-      </c>
-      <c r="B25" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C25" s="32">
-        <f>'Récap Site 2025'!E66</f>
-        <v/>
-      </c>
-      <c r="D25" s="32">
-        <f>B25*C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="33">
-        <f>Paramètres!$H$7/365</f>
-        <v/>
-      </c>
-      <c r="F25" s="32">
-        <f>D25*E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15.05" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>Gaz</t>
-        </is>
-      </c>
-      <c r="B26" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C26" s="32">
-        <f>'Récap Site 2025'!E69</f>
-        <v/>
-      </c>
-      <c r="D26" s="32">
-        <f>B26*C26</f>
-        <v/>
-      </c>
-      <c r="E26" s="33">
-        <f>Paramètres!$H$7/365</f>
-        <v/>
-      </c>
-      <c r="F26" s="32">
-        <f>D26*E26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — FLUIDES</t>
-        </is>
-      </c>
-      <c r="C27" s="8">
-        <f>SUM(C23:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>SUM(D23:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="8">
-        <f>SUM(F23:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TAXES</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.05" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Taxe Bureau &amp; Stationnement</t>
-        </is>
-      </c>
-      <c r="B29" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C29" s="32">
-        <f>'Récap Site 2025'!E73</f>
-        <v/>
-      </c>
-      <c r="D29" s="32">
-        <f>B29*C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F29" s="32">
-        <f>D29*E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TAXES</t>
-        </is>
-      </c>
-      <c r="C30" s="8">
-        <f>SUM(C29:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D29:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="8">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>HONORAIRES</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15.05" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>Honoraires Divers</t>
-        </is>
-      </c>
-      <c r="B32" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C32" s="32">
-        <f>'Récap Site 2025'!E77</f>
-        <v/>
-      </c>
-      <c r="D32" s="32">
-        <f>B32*C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F32" s="32">
-        <f>D32*E32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+        <f>IF(D24="","",D24*E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Sous-total — HONORAIRES</t>
         </is>
       </c>
-      <c r="C33" s="8">
-        <f>SUM(C32:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>SUM(D32:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="8">
-        <f>SUM(F32:F32)</f>
-        <v/>
+      <c r="C25" s="8">
+        <f>SUM(C24:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="8">
+        <f>SUM(D24:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="8">
+        <f>SUM(F24:F24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="7.55" customHeight="1"/>
+    <row r="27" ht="21.75" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
+        </is>
+      </c>
+      <c r="C27" s="11">
+        <f>C9+C14+C17+C20+C25</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>D9+D14+D17+D20+D25</f>
+        <v/>
+      </c>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="11">
+        <f>F9+F14+F17+F20+F25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="7.55" customHeight="1"/>
+    <row r="29" ht="19.55" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Provisions pour charges versées</t>
+        </is>
+      </c>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Montant annuel (€)</t>
+        </is>
+      </c>
+      <c r="E29" s="38" t="n"/>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>Montant locataire (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.8" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1er trimestre (T1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.8" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2e trimestre (T2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.8" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3e trimestre (T3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.8" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4e trimestre (T4)</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TRAVAUX</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15.05" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>Entretien Courant</t>
-        </is>
-      </c>
-      <c r="B35" s="31">
-        <f>Paramètres!$C$7/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C35" s="32">
-        <f>'Récap Site 2025'!E81</f>
-        <v/>
-      </c>
-      <c r="D35" s="32">
-        <f>B35*C35</f>
-        <v/>
-      </c>
-      <c r="E35" s="33">
-        <f>Paramètres!$J$7/365</f>
-        <v/>
-      </c>
-      <c r="F35" s="32">
-        <f>D35*E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TRAVAUX</t>
-        </is>
-      </c>
-      <c r="C36" s="8">
-        <f>SUM(C35:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="8">
-        <f>SUM(D35:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="8">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
-        </is>
-      </c>
-      <c r="C39" s="14">
-        <f>C21+C27+C30+C33+C36</f>
-        <v/>
-      </c>
-      <c r="D39" s="14">
-        <f>D21+D27+D30+D33+D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="14">
-        <f>F21+F27+F30+F33+F36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="7.55" customHeight="1"/>
-    <row r="41" ht="19.55" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Provisions pour charges versées</t>
-        </is>
-      </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="26" t="inlineStr">
-        <is>
-          <t>Montant annuel (€)</t>
-        </is>
-      </c>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>Montant locataire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15.8" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1er trimestre (T1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15.8" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2e trimestre (T2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15.8" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3e trimestre (T3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15.8" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4e trimestre (T4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D46" s="8">
-        <f>SUM(D42:D45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="8">
-        <f>SUM(F42:F45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="7.55" customHeight="1"/>
-    <row r="48" ht="21.75" customHeight="1">
-      <c r="A48" s="37">
-        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D48" s="38">
-        <f>D39-D46</f>
-        <v/>
-      </c>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="38">
-        <f>F39-F46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="27.75" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="D34" s="8">
+        <f>SUM(D30:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="8">
+        <f>SUM(F30:F33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="7.55" customHeight="1"/>
+    <row r="36" ht="21.75" customHeight="1">
+      <c r="A36" s="39">
+        <f>IF(F27-F34&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D36" s="40">
+        <f>D27-D34</f>
+        <v/>
+      </c>
+      <c r="E36" s="38" t="n"/>
+      <c r="F36" s="40">
+        <f>F27-F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="27.75" customHeight="1">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A50:F50"/>
+  <mergeCells count="20">
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3395,7 +3244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3458,7 +3307,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>CHARGES SITE — MEAUX PN01</t>
         </is>
@@ -3482,7 +3331,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récap Site 2025'!E7</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -3501,7 +3350,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -3509,7 +3358,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récap Site 2025'!E34</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -3525,126 +3374,53 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.05" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Vérifications règlementaires</t>
-        </is>
-      </c>
-      <c r="B9" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>'Récap Site 2025'!E10</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>Ascenseur</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>'Récap Site 2025'!E13</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>Chaufferie</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>'Récap Site 2025'!E16</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>Désenfumage</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>'Récap Site 2025'!E19</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>D12*E12</f>
-        <v/>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D7:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="8">
+        <f>SUM(F7:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CHARGES BÂTIMENT — MEAUX II</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>FLUIDES</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B13" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récap Site 2025'!E22</f>
+        <f>'Récap MEAUX II 2025'!E7</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -3652,7 +3428,7 @@
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>Paramètres!$J$8/365</f>
+        <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
       <c r="F13" s="32">
@@ -3663,15 +3439,15 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B14" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récap Site 2025'!E25</f>
+        <f>'Récap MEAUX II 2025'!E10</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -3679,7 +3455,7 @@
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>Paramètres!$J$8/365</f>
+        <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
       <c r="F14" s="32">
@@ -3690,15 +3466,15 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B15" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récap Site 2025'!E28</f>
+        <f>'Récap MEAUX II 2025'!E13</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -3706,7 +3482,7 @@
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>Paramètres!$J$8/365</f>
+        <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
       <c r="F15" s="32">
@@ -3717,15 +3493,15 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Gaz</t>
         </is>
       </c>
       <c r="B16" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récap Site 2025'!E31</f>
+        <f>'Récap MEAUX II 2025'!E16</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -3733,7 +3509,7 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>Paramètres!$J$8/365</f>
+        <f>Paramètres!$H$8/365</f>
         <v/>
       </c>
       <c r="F16" s="32">
@@ -3741,72 +3517,45 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-      <c r="B17" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>'Récap Site 2025'!E37</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>'Récap Site 2025'!E40</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="33">
-        <f>Paramètres!$J$8/365</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>D18*E18</f>
-        <v/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="8">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>Honoraires Divers</t>
         </is>
       </c>
       <c r="B19" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récap Site 2025'!E43</f>
+        <f>'Récap MEAUX II 2025'!E20</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -3822,126 +3571,99 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Toiture</t>
-        </is>
-      </c>
-      <c r="B20" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C20" s="32">
-        <f>'Récap Site 2025'!E46</f>
-        <v/>
-      </c>
-      <c r="D20" s="32">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="33">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — HONORAIRES</t>
+        </is>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>SUM(D19:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="8">
+        <f>SUM(F19:F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TRAVAUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Entretien Courant</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>'Récap MEAUX II 2025'!E24</f>
+        <v/>
+      </c>
+      <c r="D22" s="32">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
         <f>Paramètres!$J$8/365</f>
         <v/>
       </c>
-      <c r="F20" s="32">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — CONTRAT MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>SUM(C7:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8">
-        <f>SUM(D7:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="8">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FLUIDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B23" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C23" s="32">
-        <f>'Récap Site 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D23" s="32">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="33">
-        <f>Paramètres!$H$8/365</f>
-        <v/>
-      </c>
-      <c r="F23" s="32">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>Eau</t>
-        </is>
-      </c>
-      <c r="B24" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C24" s="32">
-        <f>'Récap Site 2025'!E63</f>
-        <v/>
-      </c>
-      <c r="D24" s="32">
-        <f>B24*C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="33">
-        <f>Paramètres!$H$8/365</f>
-        <v/>
-      </c>
-      <c r="F24" s="32">
-        <f>D24*E24</f>
-        <v/>
+      <c r="F22" s="32">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TRAVAUX</t>
+        </is>
+      </c>
+      <c r="C23" s="8">
+        <f>SUM(C22:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>SUM(D22:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="8">
+        <f>SUM(F22:F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>CONTRAT MAINTENANCE</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B25" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récap Site 2025'!E66</f>
+        <f>'Récap MEAUX II 2025'!E28</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -3949,7 +3671,7 @@
         <v/>
       </c>
       <c r="E25" s="33">
-        <f>Paramètres!$H$8/365</f>
+        <f>Paramètres!$J$8/365</f>
         <v/>
       </c>
       <c r="F25" s="32">
@@ -3960,15 +3682,15 @@
     <row r="26" ht="15.05" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B26" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C26" s="32">
-        <f>'Récap Site 2025'!E69</f>
+        <f>'Récap MEAUX II 2025'!E31</f>
         <v/>
       </c>
       <c r="D26" s="32">
@@ -3976,7 +3698,7 @@
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>Paramètres!$H$8/365</f>
+        <f>Paramètres!$J$8/365</f>
         <v/>
       </c>
       <c r="F26" s="32">
@@ -3984,45 +3706,72 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — FLUIDES</t>
-        </is>
-      </c>
-      <c r="C27" s="8">
-        <f>SUM(C23:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>SUM(D23:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="8">
-        <f>SUM(F23:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TAXES</t>
-        </is>
+    <row r="27" ht="15.05" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Désenfumage</t>
+        </is>
+      </c>
+      <c r="B27" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C27" s="32">
+        <f>'Récap MEAUX II 2025'!E34</f>
+        <v/>
+      </c>
+      <c r="D27" s="32">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Espaces verts</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C28" s="32">
+        <f>'Récap MEAUX II 2025'!E37</f>
+        <v/>
+      </c>
+      <c r="D28" s="32">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="32">
+        <f>D28*E28</f>
+        <v/>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>Taxe Bureau &amp; Stationnement</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B29" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C29" s="32">
-        <f>'Récap Site 2025'!E73</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D29" s="32">
@@ -4038,45 +3787,72 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TAXES</t>
-        </is>
-      </c>
-      <c r="C30" s="8">
-        <f>SUM(C29:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D29:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="8">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>HONORAIRES</t>
-        </is>
+    <row r="30" ht="15.05" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Portes Coupe-Feu</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C30" s="32">
+        <f>'Récap MEAUX II 2025'!E43</f>
+        <v/>
+      </c>
+      <c r="D30" s="32">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.05" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Protection foudre</t>
+        </is>
+      </c>
+      <c r="B31" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C31" s="32">
+        <f>'Récap MEAUX II 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D31" s="32">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>D31*E31</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.05" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>Honoraires Divers</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B32" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C32" s="32">
-        <f>'Récap Site 2025'!E77</f>
+        <f>'Récap MEAUX II 2025'!E49</f>
         <v/>
       </c>
       <c r="D32" s="32">
@@ -4092,45 +3868,72 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — HONORAIRES</t>
-        </is>
-      </c>
-      <c r="C33" s="8">
-        <f>SUM(C32:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>SUM(D32:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="8">
-        <f>SUM(F32:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TRAVAUX</t>
-        </is>
+    <row r="33" ht="15.05" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Séparateur hydro.</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>'Récap MEAUX II 2025'!E52</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.05" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Sprinklers - RIA - PI - Fioul</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>'Récap MEAUX II 2025'!E55</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>B34*C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>D34*E34</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>Entretien Courant</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B35" s="31">
-        <f>Paramètres!$C$8/Paramètres!$C$3</f>
+        <f>Paramètres!$C$8/38590.0</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>'Récap Site 2025'!E81</f>
+        <f>'Récap MEAUX II 2025'!E58</f>
         <v/>
       </c>
       <c r="D35" s="32">
@@ -4146,155 +3949,293 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TRAVAUX</t>
-        </is>
-      </c>
-      <c r="C36" s="8">
-        <f>SUM(C35:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="8">
-        <f>SUM(D35:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="8">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="36" ht="15.05" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Télésurveillance</t>
+        </is>
+      </c>
+      <c r="B36" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>'Récap MEAUX II 2025'!E61</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>B36*C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F36" s="32">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15.05" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B37" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>'Récap MEAUX II 2025'!E64</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>B37*C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F37" s="32">
+        <f>D37*E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15.05" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="B38" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>'Récap MEAUX II 2025'!E67</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>B38*C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F38" s="32">
+        <f>D38*E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C39" s="8">
+        <f>SUM(C25:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>SUM(D25:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="8">
+        <f>SUM(F25:F38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>TAXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.05" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+      <c r="B41" s="31">
+        <f>Paramètres!$C$8/38590.0</f>
+        <v/>
+      </c>
+      <c r="C41" s="32">
+        <f>'Récap MEAUX II 2025'!E71</f>
+        <v/>
+      </c>
+      <c r="D41" s="32">
+        <f>B41*C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="33">
+        <f>Paramètres!$J$8/365</f>
+        <v/>
+      </c>
+      <c r="F41" s="32">
+        <f>D41*E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TAXES</t>
+        </is>
+      </c>
+      <c r="C42" s="8">
+        <f>SUM(C41:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="8">
+        <f>SUM(D41:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="8">
+        <f>SUM(F41:F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="7.55" customHeight="1"/>
+    <row r="45" ht="21.75" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C39" s="14">
-        <f>C21+C27+C30+C33+C36</f>
-        <v/>
-      </c>
-      <c r="D39" s="14">
-        <f>D21+D27+D30+D33+D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="14">
-        <f>F21+F27+F30+F33+F36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="7.55" customHeight="1"/>
-    <row r="41" ht="19.55" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="C45" s="11">
+        <f>C9+C17+C20+C23+C39+C42</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>D9+D17+D20+D23+D39+D42</f>
+        <v/>
+      </c>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="11">
+        <f>F9+F17+F20+F23+F39+F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="7.55" customHeight="1"/>
+    <row r="47" ht="19.55" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="48" ht="15.8" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="49" ht="15.8" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="50" ht="15.8" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="51" ht="15.8" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D46" s="8">
-        <f>SUM(D42:D45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="8">
-        <f>SUM(F42:F45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="7.55" customHeight="1"/>
-    <row r="48" ht="21.75" customHeight="1">
-      <c r="A48" s="37">
-        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D48" s="38">
-        <f>D39-D46</f>
-        <v/>
-      </c>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="38">
-        <f>F39-F46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="27.75" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="D52" s="8">
+        <f>SUM(D48:D51)</f>
+        <v/>
+      </c>
+      <c r="E52" s="34" t="n"/>
+      <c r="F52" s="8">
+        <f>SUM(F48:F51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="7.55" customHeight="1"/>
+    <row r="54" ht="21.75" customHeight="1">
+      <c r="A54" s="39">
+        <f>IF(F45-F52&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D54" s="40">
+        <f>D45-D52</f>
+        <v/>
+      </c>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="40">
+        <f>F45-F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="27.75" customHeight="1">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A50:F50"/>
+  <mergeCells count="22">
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4307,7 +4248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4370,7 +4311,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>CHARGES SITE — MEAUX PN01</t>
         </is>
@@ -4394,7 +4335,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récap Site 2025'!E7</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -4413,7 +4354,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -4421,7 +4362,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récap Site 2025'!E34</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -4437,126 +4378,53 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.05" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Vérifications règlementaires</t>
-        </is>
-      </c>
-      <c r="B9" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>'Récap Site 2025'!E10</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>Ascenseur</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>'Récap Site 2025'!E13</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>Chaufferie</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>'Récap Site 2025'!E16</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>Désenfumage</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>'Récap Site 2025'!E19</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>D12*E12</f>
-        <v/>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D7:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="8">
+        <f>SUM(F7:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CHARGES BÂTIMENT — MEAUX II</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>FLUIDES</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B13" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récap Site 2025'!E22</f>
+        <f>'Récap MEAUX II 2025'!E7</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -4564,7 +4432,7 @@
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>Paramètres!$J$9/365</f>
+        <f>Paramètres!$H$9/365</f>
         <v/>
       </c>
       <c r="F13" s="32">
@@ -4575,15 +4443,15 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B14" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récap Site 2025'!E25</f>
+        <f>'Récap MEAUX II 2025'!E10</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -4591,7 +4459,7 @@
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>Paramètres!$J$9/365</f>
+        <f>Paramètres!$H$9/365</f>
         <v/>
       </c>
       <c r="F14" s="32">
@@ -4602,15 +4470,15 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B15" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récap Site 2025'!E28</f>
+        <f>'Récap MEAUX II 2025'!E13</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -4618,7 +4486,7 @@
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>Paramètres!$J$9/365</f>
+        <f>Paramètres!$H$9/365</f>
         <v/>
       </c>
       <c r="F15" s="32">
@@ -4629,15 +4497,15 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Gaz</t>
         </is>
       </c>
       <c r="B16" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récap Site 2025'!E31</f>
+        <f>'Récap MEAUX II 2025'!E16</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -4645,7 +4513,7 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>Paramètres!$J$9/365</f>
+        <f>Paramètres!$H$9/365</f>
         <v/>
       </c>
       <c r="F16" s="32">
@@ -4653,72 +4521,45 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-      <c r="B17" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>'Récap Site 2025'!E37</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>'Récap Site 2025'!E40</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="33">
-        <f>Paramètres!$J$9/365</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>D18*E18</f>
-        <v/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="8">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>Honoraires Divers</t>
         </is>
       </c>
       <c r="B19" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récap Site 2025'!E43</f>
+        <f>'Récap MEAUX II 2025'!E20</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -4734,126 +4575,99 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Toiture</t>
-        </is>
-      </c>
-      <c r="B20" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C20" s="32">
-        <f>'Récap Site 2025'!E46</f>
-        <v/>
-      </c>
-      <c r="D20" s="32">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="33">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — HONORAIRES</t>
+        </is>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>SUM(D19:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="8">
+        <f>SUM(F19:F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TRAVAUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Entretien Courant</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>'Récap MEAUX II 2025'!E24</f>
+        <v/>
+      </c>
+      <c r="D22" s="32">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
         <f>Paramètres!$J$9/365</f>
         <v/>
       </c>
-      <c r="F20" s="32">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — CONTRAT MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>SUM(C7:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8">
-        <f>SUM(D7:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="8">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FLUIDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B23" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C23" s="32">
-        <f>'Récap Site 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D23" s="32">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="33">
-        <f>Paramètres!$H$9/365</f>
-        <v/>
-      </c>
-      <c r="F23" s="32">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>Eau</t>
-        </is>
-      </c>
-      <c r="B24" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C24" s="32">
-        <f>'Récap Site 2025'!E63</f>
-        <v/>
-      </c>
-      <c r="D24" s="32">
-        <f>B24*C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="33">
-        <f>Paramètres!$H$9/365</f>
-        <v/>
-      </c>
-      <c r="F24" s="32">
-        <f>D24*E24</f>
-        <v/>
+      <c r="F22" s="32">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TRAVAUX</t>
+        </is>
+      </c>
+      <c r="C23" s="8">
+        <f>SUM(C22:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>SUM(D22:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="8">
+        <f>SUM(F22:F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>CONTRAT MAINTENANCE</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B25" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récap Site 2025'!E66</f>
+        <f>'Récap MEAUX II 2025'!E28</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -4861,7 +4675,7 @@
         <v/>
       </c>
       <c r="E25" s="33">
-        <f>Paramètres!$H$9/365</f>
+        <f>Paramètres!$J$9/365</f>
         <v/>
       </c>
       <c r="F25" s="32">
@@ -4872,15 +4686,15 @@
     <row r="26" ht="15.05" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B26" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C26" s="32">
-        <f>'Récap Site 2025'!E69</f>
+        <f>'Récap MEAUX II 2025'!E31</f>
         <v/>
       </c>
       <c r="D26" s="32">
@@ -4888,7 +4702,7 @@
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>Paramètres!$H$9/365</f>
+        <f>Paramètres!$J$9/365</f>
         <v/>
       </c>
       <c r="F26" s="32">
@@ -4896,45 +4710,72 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — FLUIDES</t>
-        </is>
-      </c>
-      <c r="C27" s="8">
-        <f>SUM(C23:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>SUM(D23:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="8">
-        <f>SUM(F23:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TAXES</t>
-        </is>
+    <row r="27" ht="15.05" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Désenfumage</t>
+        </is>
+      </c>
+      <c r="B27" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C27" s="32">
+        <f>'Récap MEAUX II 2025'!E34</f>
+        <v/>
+      </c>
+      <c r="D27" s="32">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Espaces verts</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C28" s="32">
+        <f>'Récap MEAUX II 2025'!E37</f>
+        <v/>
+      </c>
+      <c r="D28" s="32">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="32">
+        <f>D28*E28</f>
+        <v/>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>Taxe Bureau &amp; Stationnement</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B29" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C29" s="32">
-        <f>'Récap Site 2025'!E73</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D29" s="32">
@@ -4950,45 +4791,72 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TAXES</t>
-        </is>
-      </c>
-      <c r="C30" s="8">
-        <f>SUM(C29:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D29:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="8">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>HONORAIRES</t>
-        </is>
+    <row r="30" ht="15.05" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Portes Coupe-Feu</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C30" s="32">
+        <f>'Récap MEAUX II 2025'!E43</f>
+        <v/>
+      </c>
+      <c r="D30" s="32">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.05" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Protection foudre</t>
+        </is>
+      </c>
+      <c r="B31" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C31" s="32">
+        <f>'Récap MEAUX II 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D31" s="32">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>D31*E31</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.05" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>Honoraires Divers</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B32" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C32" s="32">
-        <f>'Récap Site 2025'!E77</f>
+        <f>'Récap MEAUX II 2025'!E49</f>
         <v/>
       </c>
       <c r="D32" s="32">
@@ -5004,45 +4872,72 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — HONORAIRES</t>
-        </is>
-      </c>
-      <c r="C33" s="8">
-        <f>SUM(C32:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>SUM(D32:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="8">
-        <f>SUM(F32:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TRAVAUX</t>
-        </is>
+    <row r="33" ht="15.05" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Séparateur hydro.</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>'Récap MEAUX II 2025'!E52</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.05" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Sprinklers - RIA - PI - Fioul</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>'Récap MEAUX II 2025'!E55</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>B34*C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>D34*E34</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>Entretien Courant</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B35" s="31">
-        <f>Paramètres!$C$9/Paramètres!$C$3</f>
+        <f>Paramètres!$C$9/38590.0</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>'Récap Site 2025'!E81</f>
+        <f>'Récap MEAUX II 2025'!E58</f>
         <v/>
       </c>
       <c r="D35" s="32">
@@ -5058,155 +4953,293 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TRAVAUX</t>
-        </is>
-      </c>
-      <c r="C36" s="8">
-        <f>SUM(C35:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="8">
-        <f>SUM(D35:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="8">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="36" ht="15.05" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Télésurveillance</t>
+        </is>
+      </c>
+      <c r="B36" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>'Récap MEAUX II 2025'!E61</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>B36*C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F36" s="32">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15.05" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B37" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>'Récap MEAUX II 2025'!E64</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>B37*C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F37" s="32">
+        <f>D37*E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15.05" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="B38" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>'Récap MEAUX II 2025'!E67</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>B38*C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F38" s="32">
+        <f>D38*E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C39" s="8">
+        <f>SUM(C25:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>SUM(D25:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="8">
+        <f>SUM(F25:F38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>TAXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.05" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+      <c r="B41" s="31">
+        <f>Paramètres!$C$9/38590.0</f>
+        <v/>
+      </c>
+      <c r="C41" s="32">
+        <f>'Récap MEAUX II 2025'!E71</f>
+        <v/>
+      </c>
+      <c r="D41" s="32">
+        <f>B41*C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="33">
+        <f>Paramètres!$J$9/365</f>
+        <v/>
+      </c>
+      <c r="F41" s="32">
+        <f>D41*E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TAXES</t>
+        </is>
+      </c>
+      <c r="C42" s="8">
+        <f>SUM(C41:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="8">
+        <f>SUM(D41:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="8">
+        <f>SUM(F41:F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="7.55" customHeight="1"/>
+    <row r="45" ht="21.75" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C39" s="14">
-        <f>C21+C27+C30+C33+C36</f>
-        <v/>
-      </c>
-      <c r="D39" s="14">
-        <f>D21+D27+D30+D33+D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="14">
-        <f>F21+F27+F30+F33+F36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="7.55" customHeight="1"/>
-    <row r="41" ht="19.55" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="C45" s="11">
+        <f>C9+C17+C20+C23+C39+C42</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>D9+D17+D20+D23+D39+D42</f>
+        <v/>
+      </c>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="11">
+        <f>F9+F17+F20+F23+F39+F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="7.55" customHeight="1"/>
+    <row r="47" ht="19.55" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="48" ht="15.8" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="49" ht="15.8" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="50" ht="15.8" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="51" ht="15.8" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D46" s="8">
-        <f>SUM(D42:D45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="8">
-        <f>SUM(F42:F45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="7.55" customHeight="1"/>
-    <row r="48" ht="21.75" customHeight="1">
-      <c r="A48" s="37">
-        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D48" s="38">
-        <f>D39-D46</f>
-        <v/>
-      </c>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="38">
-        <f>F39-F46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="27.75" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="D52" s="8">
+        <f>SUM(D48:D51)</f>
+        <v/>
+      </c>
+      <c r="E52" s="34" t="n"/>
+      <c r="F52" s="8">
+        <f>SUM(F48:F51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="7.55" customHeight="1"/>
+    <row r="54" ht="21.75" customHeight="1">
+      <c r="A54" s="39">
+        <f>IF(F45-F52&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D54" s="40">
+        <f>D45-D52</f>
+        <v/>
+      </c>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="40">
+        <f>F45-F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="27.75" customHeight="1">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A50:F50"/>
+  <mergeCells count="22">
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5219,7 +5252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5282,7 +5315,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>CHARGES SITE — MEAUX PN01</t>
         </is>
@@ -5306,7 +5339,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récap Site 2025'!E7</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -5325,7 +5358,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -5333,7 +5366,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récap Site 2025'!E34</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -5349,126 +5382,53 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.05" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Vérifications règlementaires</t>
-        </is>
-      </c>
-      <c r="B9" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>'Récap Site 2025'!E10</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>Ascenseur</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>'Récap Site 2025'!E13</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>Chaufferie</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>'Récap Site 2025'!E16</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>Désenfumage</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>'Récap Site 2025'!E19</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>D12*E12</f>
-        <v/>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D7:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="8">
+        <f>SUM(F7:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CHARGES BÂTIMENT — MEAUX II</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>FLUIDES</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B13" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récap Site 2025'!E22</f>
+        <f>'Récap MEAUX II 2025'!E7</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -5476,7 +5436,7 @@
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>Paramètres!$J$10/365</f>
+        <f>Paramètres!$H$10/365</f>
         <v/>
       </c>
       <c r="F13" s="32">
@@ -5487,15 +5447,15 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B14" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récap Site 2025'!E25</f>
+        <f>'Récap MEAUX II 2025'!E10</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -5503,7 +5463,7 @@
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>Paramètres!$J$10/365</f>
+        <f>Paramètres!$H$10/365</f>
         <v/>
       </c>
       <c r="F14" s="32">
@@ -5514,15 +5474,15 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B15" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récap Site 2025'!E28</f>
+        <f>'Récap MEAUX II 2025'!E13</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -5530,7 +5490,7 @@
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>Paramètres!$J$10/365</f>
+        <f>Paramètres!$H$10/365</f>
         <v/>
       </c>
       <c r="F15" s="32">
@@ -5541,15 +5501,15 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Gaz</t>
         </is>
       </c>
       <c r="B16" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récap Site 2025'!E31</f>
+        <f>'Récap MEAUX II 2025'!E16</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -5557,7 +5517,7 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>Paramètres!$J$10/365</f>
+        <f>Paramètres!$H$10/365</f>
         <v/>
       </c>
       <c r="F16" s="32">
@@ -5565,72 +5525,45 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-      <c r="B17" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>'Récap Site 2025'!E37</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>'Récap Site 2025'!E40</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="33">
-        <f>Paramètres!$J$10/365</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>D18*E18</f>
-        <v/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="8">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>Honoraires Divers</t>
         </is>
       </c>
       <c r="B19" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récap Site 2025'!E43</f>
+        <f>'Récap MEAUX II 2025'!E20</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -5646,126 +5579,99 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Toiture</t>
-        </is>
-      </c>
-      <c r="B20" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C20" s="32">
-        <f>'Récap Site 2025'!E46</f>
-        <v/>
-      </c>
-      <c r="D20" s="32">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="33">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — HONORAIRES</t>
+        </is>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>SUM(D19:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="8">
+        <f>SUM(F19:F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TRAVAUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Entretien Courant</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>'Récap MEAUX II 2025'!E24</f>
+        <v/>
+      </c>
+      <c r="D22" s="32">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
         <f>Paramètres!$J$10/365</f>
         <v/>
       </c>
-      <c r="F20" s="32">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — CONTRAT MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>SUM(C7:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8">
-        <f>SUM(D7:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="8">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FLUIDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B23" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C23" s="32">
-        <f>'Récap Site 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D23" s="32">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="33">
-        <f>Paramètres!$H$10/365</f>
-        <v/>
-      </c>
-      <c r="F23" s="32">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>Eau</t>
-        </is>
-      </c>
-      <c r="B24" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C24" s="32">
-        <f>'Récap Site 2025'!E63</f>
-        <v/>
-      </c>
-      <c r="D24" s="32">
-        <f>B24*C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="33">
-        <f>Paramètres!$H$10/365</f>
-        <v/>
-      </c>
-      <c r="F24" s="32">
-        <f>D24*E24</f>
-        <v/>
+      <c r="F22" s="32">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TRAVAUX</t>
+        </is>
+      </c>
+      <c r="C23" s="8">
+        <f>SUM(C22:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>SUM(D22:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="8">
+        <f>SUM(F22:F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>CONTRAT MAINTENANCE</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B25" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récap Site 2025'!E66</f>
+        <f>'Récap MEAUX II 2025'!E28</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -5773,7 +5679,7 @@
         <v/>
       </c>
       <c r="E25" s="33">
-        <f>Paramètres!$H$10/365</f>
+        <f>Paramètres!$J$10/365</f>
         <v/>
       </c>
       <c r="F25" s="32">
@@ -5784,15 +5690,15 @@
     <row r="26" ht="15.05" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B26" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C26" s="32">
-        <f>'Récap Site 2025'!E69</f>
+        <f>'Récap MEAUX II 2025'!E31</f>
         <v/>
       </c>
       <c r="D26" s="32">
@@ -5800,7 +5706,7 @@
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>Paramètres!$H$10/365</f>
+        <f>Paramètres!$J$10/365</f>
         <v/>
       </c>
       <c r="F26" s="32">
@@ -5808,45 +5714,72 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — FLUIDES</t>
-        </is>
-      </c>
-      <c r="C27" s="8">
-        <f>SUM(C23:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>SUM(D23:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="8">
-        <f>SUM(F23:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TAXES</t>
-        </is>
+    <row r="27" ht="15.05" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Désenfumage</t>
+        </is>
+      </c>
+      <c r="B27" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C27" s="32">
+        <f>'Récap MEAUX II 2025'!E34</f>
+        <v/>
+      </c>
+      <c r="D27" s="32">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Espaces verts</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C28" s="32">
+        <f>'Récap MEAUX II 2025'!E37</f>
+        <v/>
+      </c>
+      <c r="D28" s="32">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="32">
+        <f>D28*E28</f>
+        <v/>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>Taxe Bureau &amp; Stationnement</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B29" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C29" s="32">
-        <f>'Récap Site 2025'!E73</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D29" s="32">
@@ -5862,45 +5795,72 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TAXES</t>
-        </is>
-      </c>
-      <c r="C30" s="8">
-        <f>SUM(C29:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D29:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="8">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>HONORAIRES</t>
-        </is>
+    <row r="30" ht="15.05" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Portes Coupe-Feu</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C30" s="32">
+        <f>'Récap MEAUX II 2025'!E43</f>
+        <v/>
+      </c>
+      <c r="D30" s="32">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.05" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Protection foudre</t>
+        </is>
+      </c>
+      <c r="B31" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C31" s="32">
+        <f>'Récap MEAUX II 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D31" s="32">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>D31*E31</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.05" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>Honoraires Divers</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B32" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C32" s="32">
-        <f>'Récap Site 2025'!E77</f>
+        <f>'Récap MEAUX II 2025'!E49</f>
         <v/>
       </c>
       <c r="D32" s="32">
@@ -5916,45 +5876,72 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — HONORAIRES</t>
-        </is>
-      </c>
-      <c r="C33" s="8">
-        <f>SUM(C32:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>SUM(D32:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="8">
-        <f>SUM(F32:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TRAVAUX</t>
-        </is>
+    <row r="33" ht="15.05" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Séparateur hydro.</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>'Récap MEAUX II 2025'!E52</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.05" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Sprinklers - RIA - PI - Fioul</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>'Récap MEAUX II 2025'!E55</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>B34*C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>D34*E34</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>Entretien Courant</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B35" s="31">
-        <f>Paramètres!$C$10/Paramètres!$C$3</f>
+        <f>Paramètres!$C$10/38590.0</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>'Récap Site 2025'!E81</f>
+        <f>'Récap MEAUX II 2025'!E58</f>
         <v/>
       </c>
       <c r="D35" s="32">
@@ -5970,155 +5957,293 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TRAVAUX</t>
-        </is>
-      </c>
-      <c r="C36" s="8">
-        <f>SUM(C35:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="8">
-        <f>SUM(D35:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="8">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="36" ht="15.05" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Télésurveillance</t>
+        </is>
+      </c>
+      <c r="B36" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>'Récap MEAUX II 2025'!E61</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>B36*C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F36" s="32">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15.05" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B37" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>'Récap MEAUX II 2025'!E64</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>B37*C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F37" s="32">
+        <f>D37*E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15.05" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="B38" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>'Récap MEAUX II 2025'!E67</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>B38*C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F38" s="32">
+        <f>D38*E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C39" s="8">
+        <f>SUM(C25:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>SUM(D25:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="8">
+        <f>SUM(F25:F38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>TAXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.05" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+      <c r="B41" s="31">
+        <f>Paramètres!$C$10/38590.0</f>
+        <v/>
+      </c>
+      <c r="C41" s="32">
+        <f>'Récap MEAUX II 2025'!E71</f>
+        <v/>
+      </c>
+      <c r="D41" s="32">
+        <f>B41*C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="33">
+        <f>Paramètres!$J$10/365</f>
+        <v/>
+      </c>
+      <c r="F41" s="32">
+        <f>D41*E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TAXES</t>
+        </is>
+      </c>
+      <c r="C42" s="8">
+        <f>SUM(C41:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="8">
+        <f>SUM(D41:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="8">
+        <f>SUM(F41:F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="7.55" customHeight="1"/>
+    <row r="45" ht="21.75" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C39" s="14">
-        <f>C21+C27+C30+C33+C36</f>
-        <v/>
-      </c>
-      <c r="D39" s="14">
-        <f>D21+D27+D30+D33+D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="14">
-        <f>F21+F27+F30+F33+F36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="7.55" customHeight="1"/>
-    <row r="41" ht="19.55" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="C45" s="11">
+        <f>C9+C17+C20+C23+C39+C42</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>D9+D17+D20+D23+D39+D42</f>
+        <v/>
+      </c>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="11">
+        <f>F9+F17+F20+F23+F39+F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="7.55" customHeight="1"/>
+    <row r="47" ht="19.55" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="48" ht="15.8" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="49" ht="15.8" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="50" ht="15.8" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="51" ht="15.8" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D46" s="8">
-        <f>SUM(D42:D45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="8">
-        <f>SUM(F42:F45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="7.55" customHeight="1"/>
-    <row r="48" ht="21.75" customHeight="1">
-      <c r="A48" s="37">
-        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D48" s="38">
-        <f>D39-D46</f>
-        <v/>
-      </c>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="38">
-        <f>F39-F46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="27.75" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="D52" s="8">
+        <f>SUM(D48:D51)</f>
+        <v/>
+      </c>
+      <c r="E52" s="34" t="n"/>
+      <c r="F52" s="8">
+        <f>SUM(F48:F51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="7.55" customHeight="1"/>
+    <row r="54" ht="21.75" customHeight="1">
+      <c r="A54" s="39">
+        <f>IF(F45-F52&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D54" s="40">
+        <f>D45-D52</f>
+        <v/>
+      </c>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="40">
+        <f>F45-F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="27.75" customHeight="1">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A50:F50"/>
+  <mergeCells count="22">
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6131,7 +6256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6194,7 +6319,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>CHARGES SITE — MEAUX PN01</t>
         </is>
@@ -6218,7 +6343,7 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>'Récap Site 2025'!E7</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D7" s="32">
@@ -6237,7 +6362,7 @@
     <row r="8" ht="15.05" customHeight="1">
       <c r="A8" s="30" t="inlineStr">
         <is>
-          <t>Séparateur hydro.</t>
+          <t>Vérifications règlementaires</t>
         </is>
       </c>
       <c r="B8" s="31">
@@ -6245,7 +6370,7 @@
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>'Récap Site 2025'!E34</f>
+        <f>'Récap MEAUX II 2025'!E67</f>
         <v/>
       </c>
       <c r="D8" s="32">
@@ -6261,126 +6386,53 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15.05" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>Vérifications règlementaires</t>
-        </is>
-      </c>
-      <c r="B9" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C9" s="32">
-        <f>'Récap Site 2025'!E10</f>
-        <v/>
-      </c>
-      <c r="D9" s="32">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F9" s="32">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15.05" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>Ascenseur</t>
-        </is>
-      </c>
-      <c r="B10" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>'Récap Site 2025'!E13</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.05" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>Chaufferie</t>
-        </is>
-      </c>
-      <c r="B11" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>'Récap Site 2025'!E16</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15.05" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>Désenfumage</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>'Récap Site 2025'!E19</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
-        <f>D12*E12</f>
-        <v/>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C9" s="8">
+        <f>SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D7:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="8">
+        <f>SUM(F7:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>CHARGES BÂTIMENT — MEAUX II</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>FLUIDES</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="15.05" customHeight="1">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>Espaces verts</t>
+          <t>Eau</t>
         </is>
       </c>
       <c r="B13" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C13" s="32">
-        <f>'Récap Site 2025'!E22</f>
+        <f>'Récap MEAUX II 2025'!E7</f>
         <v/>
       </c>
       <c r="D13" s="32">
@@ -6388,7 +6440,7 @@
         <v/>
       </c>
       <c r="E13" s="33">
-        <f>Paramètres!$J$11/365</f>
+        <f>Paramètres!$H$11/365</f>
         <v/>
       </c>
       <c r="F13" s="32">
@@ -6399,15 +6451,15 @@
     <row r="14" ht="15.05" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>Portes Coupe-Feu</t>
+          <t>Eau - Incendie</t>
         </is>
       </c>
       <c r="B14" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C14" s="32">
-        <f>'Récap Site 2025'!E25</f>
+        <f>'Récap MEAUX II 2025'!E10</f>
         <v/>
       </c>
       <c r="D14" s="32">
@@ -6415,7 +6467,7 @@
         <v/>
       </c>
       <c r="E14" s="33">
-        <f>Paramètres!$J$11/365</f>
+        <f>Paramètres!$H$11/365</f>
         <v/>
       </c>
       <c r="F14" s="32">
@@ -6426,15 +6478,15 @@
     <row r="15" ht="15.05" customHeight="1">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>Protection foudre</t>
+          <t>Electricité</t>
         </is>
       </c>
       <c r="B15" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C15" s="32">
-        <f>'Récap Site 2025'!E28</f>
+        <f>'Récap MEAUX II 2025'!E13</f>
         <v/>
       </c>
       <c r="D15" s="32">
@@ -6442,7 +6494,7 @@
         <v/>
       </c>
       <c r="E15" s="33">
-        <f>Paramètres!$J$11/365</f>
+        <f>Paramètres!$H$11/365</f>
         <v/>
       </c>
       <c r="F15" s="32">
@@ -6453,15 +6505,15 @@
     <row r="16" ht="15.05" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>Quais &amp; Portes sectionnelles</t>
+          <t>Gaz</t>
         </is>
       </c>
       <c r="B16" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>'Récap Site 2025'!E31</f>
+        <f>'Récap MEAUX II 2025'!E16</f>
         <v/>
       </c>
       <c r="D16" s="32">
@@ -6469,7 +6521,7 @@
         <v/>
       </c>
       <c r="E16" s="33">
-        <f>Paramètres!$J$11/365</f>
+        <f>Paramètres!$H$11/365</f>
         <v/>
       </c>
       <c r="F16" s="32">
@@ -6477,72 +6529,45 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15.05" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>Sprinklers - RIA - PI - Fioul</t>
-        </is>
-      </c>
-      <c r="B17" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C17" s="32">
-        <f>'Récap Site 2025'!E37</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15.05" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C18" s="32">
-        <f>'Récap Site 2025'!E40</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="33">
-        <f>Paramètres!$J$11/365</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>D18*E18</f>
-        <v/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — FLUIDES</t>
+        </is>
+      </c>
+      <c r="C17" s="8">
+        <f>SUM(C13:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>SUM(D13:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="8">
+        <f>SUM(F13:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HONORAIRES</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="15.05" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>Télésurveillance</t>
+          <t>Honoraires Divers</t>
         </is>
       </c>
       <c r="B19" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C19" s="32">
-        <f>'Récap Site 2025'!E43</f>
+        <f>'Récap MEAUX II 2025'!E20</f>
         <v/>
       </c>
       <c r="D19" s="32">
@@ -6558,126 +6583,99 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.05" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Toiture</t>
-        </is>
-      </c>
-      <c r="B20" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C20" s="32">
-        <f>'Récap Site 2025'!E46</f>
-        <v/>
-      </c>
-      <c r="D20" s="32">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="33">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — HONORAIRES</t>
+        </is>
+      </c>
+      <c r="C20" s="8">
+        <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="8">
+        <f>SUM(D19:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="8">
+        <f>SUM(F19:F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TRAVAUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.05" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Entretien Courant</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>'Récap MEAUX II 2025'!E24</f>
+        <v/>
+      </c>
+      <c r="D22" s="32">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="33">
         <f>Paramètres!$J$11/365</f>
         <v/>
       </c>
-      <c r="F20" s="32">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — CONTRAT MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>SUM(C7:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="8">
-        <f>SUM(D7:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="8">
-        <f>SUM(F7:F20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FLUIDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.05" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>Electricité</t>
-        </is>
-      </c>
-      <c r="B23" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C23" s="32">
-        <f>'Récap Site 2025'!E60</f>
-        <v/>
-      </c>
-      <c r="D23" s="32">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="33">
-        <f>Paramètres!$H$11/365</f>
-        <v/>
-      </c>
-      <c r="F23" s="32">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15.05" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>Eau</t>
-        </is>
-      </c>
-      <c r="B24" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
-        <v/>
-      </c>
-      <c r="C24" s="32">
-        <f>'Récap Site 2025'!E63</f>
-        <v/>
-      </c>
-      <c r="D24" s="32">
-        <f>B24*C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="33">
-        <f>Paramètres!$H$11/365</f>
-        <v/>
-      </c>
-      <c r="F24" s="32">
-        <f>D24*E24</f>
-        <v/>
+      <c r="F22" s="32">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TRAVAUX</t>
+        </is>
+      </c>
+      <c r="C23" s="8">
+        <f>SUM(C22:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>SUM(D22:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="8">
+        <f>SUM(F22:F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>CONTRAT MAINTENANCE</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15.05" customHeight="1">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>Eau - Incendie</t>
+          <t>Ascenseur</t>
         </is>
       </c>
       <c r="B25" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C25" s="32">
-        <f>'Récap Site 2025'!E66</f>
+        <f>'Récap MEAUX II 2025'!E28</f>
         <v/>
       </c>
       <c r="D25" s="32">
@@ -6685,7 +6683,7 @@
         <v/>
       </c>
       <c r="E25" s="33">
-        <f>Paramètres!$H$11/365</f>
+        <f>Paramètres!$J$11/365</f>
         <v/>
       </c>
       <c r="F25" s="32">
@@ -6696,15 +6694,15 @@
     <row r="26" ht="15.05" customHeight="1">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>Gaz</t>
+          <t>Chaufferie</t>
         </is>
       </c>
       <c r="B26" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C26" s="32">
-        <f>'Récap Site 2025'!E69</f>
+        <f>'Récap MEAUX II 2025'!E31</f>
         <v/>
       </c>
       <c r="D26" s="32">
@@ -6712,7 +6710,7 @@
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>Paramètres!$H$11/365</f>
+        <f>Paramètres!$J$11/365</f>
         <v/>
       </c>
       <c r="F26" s="32">
@@ -6720,45 +6718,72 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — FLUIDES</t>
-        </is>
-      </c>
-      <c r="C27" s="8">
-        <f>SUM(C23:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="8">
-        <f>SUM(D23:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="8">
-        <f>SUM(F23:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>TAXES</t>
-        </is>
+    <row r="27" ht="15.05" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Désenfumage</t>
+        </is>
+      </c>
+      <c r="B27" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C27" s="32">
+        <f>'Récap MEAUX II 2025'!E34</f>
+        <v/>
+      </c>
+      <c r="D27" s="32">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15.05" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Espaces verts</t>
+        </is>
+      </c>
+      <c r="B28" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C28" s="32">
+        <f>'Récap MEAUX II 2025'!E37</f>
+        <v/>
+      </c>
+      <c r="D28" s="32">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="32">
+        <f>D28*E28</f>
+        <v/>
       </c>
     </row>
     <row r="29" ht="15.05" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>Taxe Bureau &amp; Stationnement</t>
+          <t>Portails + Barrières automatiques</t>
         </is>
       </c>
       <c r="B29" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C29" s="32">
-        <f>'Récap Site 2025'!E73</f>
+        <f>'Récap MEAUX II 2025'!E40</f>
         <v/>
       </c>
       <c r="D29" s="32">
@@ -6774,45 +6799,72 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TAXES</t>
-        </is>
-      </c>
-      <c r="C30" s="8">
-        <f>SUM(C29:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D29:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="8">
-        <f>SUM(F29:F29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>HONORAIRES</t>
-        </is>
+    <row r="30" ht="15.05" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Portes Coupe-Feu</t>
+        </is>
+      </c>
+      <c r="B30" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C30" s="32">
+        <f>'Récap MEAUX II 2025'!E43</f>
+        <v/>
+      </c>
+      <c r="D30" s="32">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15.05" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Protection foudre</t>
+        </is>
+      </c>
+      <c r="B31" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C31" s="32">
+        <f>'Récap MEAUX II 2025'!E46</f>
+        <v/>
+      </c>
+      <c r="D31" s="32">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>D31*E31</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="15.05" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>Honoraires Divers</t>
+          <t>Quais &amp; Portes sectionnelles</t>
         </is>
       </c>
       <c r="B32" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C32" s="32">
-        <f>'Récap Site 2025'!E77</f>
+        <f>'Récap MEAUX II 2025'!E49</f>
         <v/>
       </c>
       <c r="D32" s="32">
@@ -6828,45 +6880,72 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — HONORAIRES</t>
-        </is>
-      </c>
-      <c r="C33" s="8">
-        <f>SUM(C32:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="8">
-        <f>SUM(D32:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="8">
-        <f>SUM(F32:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>TRAVAUX</t>
-        </is>
+    <row r="33" ht="15.05" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Séparateur hydro.</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>'Récap MEAUX II 2025'!E52</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.05" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Sprinklers - RIA - PI - Fioul</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>'Récap MEAUX II 2025'!E55</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>B34*C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>D34*E34</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="15.05" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>Entretien Courant</t>
+          <t>SSI</t>
         </is>
       </c>
       <c r="B35" s="31">
-        <f>Paramètres!$C$11/Paramètres!$C$3</f>
+        <f>Paramètres!$C$11/38590.0</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>'Récap Site 2025'!E81</f>
+        <f>'Récap MEAUX II 2025'!E58</f>
         <v/>
       </c>
       <c r="D35" s="32">
@@ -6882,155 +6961,293 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>Sous-total — TRAVAUX</t>
-        </is>
-      </c>
-      <c r="C36" s="8">
-        <f>SUM(C35:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="8">
-        <f>SUM(D35:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="8">
-        <f>SUM(F35:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="7.55" customHeight="1"/>
-    <row r="39" ht="21.75" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="36" ht="15.05" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Télésurveillance</t>
+        </is>
+      </c>
+      <c r="B36" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>'Récap MEAUX II 2025'!E61</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>B36*C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F36" s="32">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15.05" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Toiture</t>
+        </is>
+      </c>
+      <c r="B37" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>'Récap MEAUX II 2025'!E64</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>B37*C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F37" s="32">
+        <f>D37*E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="15.05" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Vérifications règlementaires</t>
+        </is>
+      </c>
+      <c r="B38" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>'Récap MEAUX II 2025'!E67</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>B38*C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F38" s="32">
+        <f>D38*E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — CONTRAT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C39" s="8">
+        <f>SUM(C25:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>SUM(D25:D38)</f>
+        <v/>
+      </c>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="8">
+        <f>SUM(F25:F38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>TAXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.05" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Taxe Bureau &amp; Stationnement</t>
+        </is>
+      </c>
+      <c r="B41" s="31">
+        <f>Paramètres!$C$11/38590.0</f>
+        <v/>
+      </c>
+      <c r="C41" s="32">
+        <f>'Récap MEAUX II 2025'!E71</f>
+        <v/>
+      </c>
+      <c r="D41" s="32">
+        <f>B41*C41</f>
+        <v/>
+      </c>
+      <c r="E41" s="33">
+        <f>Paramètres!$J$11/365</f>
+        <v/>
+      </c>
+      <c r="F41" s="32">
+        <f>D41*E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total — TAXES</t>
+        </is>
+      </c>
+      <c r="C42" s="8">
+        <f>SUM(C41:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="8">
+        <f>SUM(D41:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="8">
+        <f>SUM(F41:F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="7.55" customHeight="1"/>
+    <row r="45" ht="21.75" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>TOTAL CHARGES RÉCUPÉRABLES RÉELLES (€ HT)</t>
         </is>
       </c>
-      <c r="C39" s="14">
-        <f>C21+C27+C30+C33+C36</f>
-        <v/>
-      </c>
-      <c r="D39" s="14">
-        <f>D21+D27+D30+D33+D36</f>
-        <v/>
-      </c>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="14">
-        <f>F21+F27+F30+F33+F36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="7.55" customHeight="1"/>
-    <row r="41" ht="19.55" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="C45" s="11">
+        <f>C9+C17+C20+C23+C39+C42</f>
+        <v/>
+      </c>
+      <c r="D45" s="11">
+        <f>D9+D17+D20+D23+D39+D42</f>
+        <v/>
+      </c>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="11">
+        <f>F9+F17+F20+F23+F39+F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="7.55" customHeight="1"/>
+    <row r="47" ht="19.55" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Provisions pour charges versées</t>
         </is>
       </c>
-      <c r="C41" s="36" t="n"/>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Montant annuel (€)</t>
         </is>
       </c>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="E47" s="38" t="n"/>
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>Montant locataire (€)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="48" ht="15.8" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  1er trimestre (T1)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="49" ht="15.8" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  2e trimestre (T2)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="50" ht="15.8" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  3e trimestre (T3)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+    <row r="51" ht="15.8" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  4e trimestre (T4)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Total provisions pour charges versées →</t>
         </is>
       </c>
-      <c r="D46" s="8">
-        <f>SUM(D42:D45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="8">
-        <f>SUM(F42:F45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="7.55" customHeight="1"/>
-    <row r="48" ht="21.75" customHeight="1">
-      <c r="A48" s="37">
-        <f>IF(F39-F46&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
-        <v/>
-      </c>
-      <c r="D48" s="38">
-        <f>D39-D46</f>
-        <v/>
-      </c>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="38">
-        <f>F39-F46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="27.75" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="D52" s="8">
+        <f>SUM(D48:D51)</f>
+        <v/>
+      </c>
+      <c r="E52" s="34" t="n"/>
+      <c r="F52" s="8">
+        <f>SUM(F48:F51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="7.55" customHeight="1"/>
+    <row r="54" ht="21.75" customHeight="1">
+      <c r="A54" s="39">
+        <f>IF(F45-F52&gt;0,"SOLDE DÉBITEUR","SOLDE CRÉDITEUR")</f>
+        <v/>
+      </c>
+      <c r="D54" s="40">
+        <f>D45-D52</f>
+        <v/>
+      </c>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="40">
+        <f>F45-F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="27.75" customHeight="1">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>ℹ  Clé répartition = surface lot ÷ surface totale site. Période = nombre de jours d'occupation ÷ 365.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A50:F50"/>
+  <mergeCells count="22">
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/regularisation_MEAUX_PN01_2025.xlsx
+++ b/regularisation_MEAUX_PN01_2025.xlsx
@@ -1465,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1988,7 +1988,7 @@
       </c>
     </row>
     <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="25.55" customHeight="1">
+    <row r="30" ht="6" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
           <t>TOTAL GÉNÉRAL — CHARGES RÉCUPÉRABLES</t>
@@ -1999,12 +1999,104 @@
         <v/>
       </c>
     </row>
+    <row r="31" ht="21.75" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>── ASSURANCE / TAXES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Assurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.05" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="15.8" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Assurance</t>
+        </is>
+      </c>
+      <c r="E34" s="10">
+        <f>E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Taxe foncière</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15.05" customHeight="1">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="15.8" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Taxe foncière</t>
+        </is>
+      </c>
+      <c r="E37" s="10">
+        <f>E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Autres taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15.05" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+    </row>
+    <row r="40" ht="15.8" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Autres taxes</t>
+        </is>
+      </c>
+      <c r="E40" s="10">
+        <f>E39</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A22:G22"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A21:D21"/>
@@ -2024,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5601,7 +5693,7 @@
       </c>
     </row>
     <row r="157" ht="6" customHeight="1"/>
-    <row r="158" ht="25.55" customHeight="1">
+    <row r="158" ht="6" customHeight="1">
       <c r="A158" s="13" t="inlineStr">
         <is>
           <t>TOTAL GÉNÉRAL — CHARGES RÉCUPÉRABLES</t>
@@ -5612,11 +5704,101 @@
         <v/>
       </c>
     </row>
+    <row r="159" ht="21.75" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>── ASSURANCE / TAXES ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Assurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="15.05" customHeight="1">
+      <c r="A161" s="6" t="inlineStr"/>
+      <c r="B161" s="11" t="n"/>
+      <c r="C161" s="11" t="n"/>
+      <c r="D161" s="11" t="n"/>
+      <c r="E161" s="8" t="n"/>
+      <c r="F161" s="8" t="n"/>
+      <c r="G161" s="8" t="n"/>
+    </row>
+    <row r="162" ht="15.8" customHeight="1">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Assurance</t>
+        </is>
+      </c>
+      <c r="E162" s="10">
+        <f>E161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Taxe foncière</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="15.05" customHeight="1">
+      <c r="A164" s="6" t="inlineStr"/>
+      <c r="B164" s="11" t="n"/>
+      <c r="C164" s="11" t="n"/>
+      <c r="D164" s="11" t="n"/>
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="8" t="n"/>
+      <c r="G164" s="8" t="n"/>
+    </row>
+    <row r="165" ht="15.8" customHeight="1">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Taxe foncière</t>
+        </is>
+      </c>
+      <c r="E165" s="10">
+        <f>E164</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Autres taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="15.05" customHeight="1">
+      <c r="A167" s="6" t="inlineStr"/>
+      <c r="B167" s="11" t="n"/>
+      <c r="C167" s="11" t="n"/>
+      <c r="D167" s="11" t="n"/>
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="8" t="n"/>
+      <c r="G167" s="8" t="n"/>
+    </row>
+    <row r="168" ht="15.8" customHeight="1">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sous-total — Autres taxes</t>
+        </is>
+      </c>
+      <c r="E168" s="10">
+        <f>E167</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="37">
+    <mergeCell ref="A159:G159"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A96:D96"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A165:D165"/>
     <mergeCell ref="A81:D81"/>
     <mergeCell ref="A156:D156"/>
     <mergeCell ref="A63:D63"/>
@@ -5631,7 +5813,9 @@
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A132:D132"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A168:D168"/>
     <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A162:D162"/>
     <mergeCell ref="A87:D87"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A128:G128"/>
